--- a/results/evaluation/bm25_candidates.xlsx
+++ b/results/evaluation/bm25_candidates.xlsx
@@ -7376,23 +7376,23 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Tìm truyện kỳ ảo</t>
+          <t>Tìm truyện tiên hiệp hơn 500 chương</t>
         </is>
       </c>
       <c r="C152" t="n">
         <v>1</v>
       </c>
       <c r="D152" t="n">
-        <v>17831</v>
+        <v>13674</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Ta Thật Muốn Khống Chế Ngươi, Hoàng Nữ Điện Hạ [Convert]</t>
+          <t>Vạn Thú Thế Gia Quật Khởi [Convert]</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Kỳ Ảo</t>
+          <t>Tiên Hiệp</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -7401,7 +7401,7 @@
         </is>
       </c>
       <c r="H152" t="n">
-        <v>9.4109</v>
+        <v>14.4187</v>
       </c>
       <c r="I152" t="inlineStr">
         <is>
@@ -7410,7 +7410,7 @@
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/17831-ta-that-muon-khong-che-nguoi-hoang-nu-dien-ha-convert</t>
+          <t>https://sitruyencv.com/story/13674-van-thu-the-gia-quat-khoi-convert</t>
         </is>
       </c>
     </row>
@@ -7422,32 +7422,32 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Tìm truyện kỳ ảo</t>
+          <t>Tìm truyện tiên hiệp hơn 500 chương</t>
         </is>
       </c>
       <c r="C153" t="n">
         <v>2</v>
       </c>
       <c r="D153" t="n">
-        <v>252</v>
+        <v>16201</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Toàn Cầu Luyện Cổ: Ta Có Thể Thôi Diễn Hợp Luyện Lộ Tuyến [Convert]</t>
+          <t>Nữ Hiệp Xin Dừng Tay [Convert]</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Kỳ Ảo</t>
+          <t>Dã Sử</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Hoàn thành</t>
+          <t>Tạm dừng</t>
         </is>
       </c>
       <c r="H153" t="n">
-        <v>8.781700000000001</v>
+        <v>10.342</v>
       </c>
       <c r="I153" t="inlineStr">
         <is>
@@ -7456,7 +7456,7 @@
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/252-toan-cau-luyen-co-ta-co-the-thoi-dien-hop-luyen-lo-tuyen-convert</t>
+          <t>https://sitruyencv.com/story/16201-nu-hiep-xin-dung-tay-convert</t>
         </is>
       </c>
     </row>
@@ -7468,23 +7468,23 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Tìm truyện kỳ ảo</t>
+          <t>Tìm truyện tiên hiệp hơn 500 chương</t>
         </is>
       </c>
       <c r="C154" t="n">
         <v>3</v>
       </c>
       <c r="D154" t="n">
-        <v>20789</v>
+        <v>9529</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Trường sinh thận trọng lộ [Dịch]</t>
+          <t>Trực Tiếp Thiết Kế Tử Vong [Convert]</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Tiên Hiệp Kỳ Duyên</t>
+          <t>Đô Thị</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
@@ -7493,7 +7493,7 @@
         </is>
       </c>
       <c r="H154" t="n">
-        <v>4.8843</v>
+        <v>7.3699</v>
       </c>
       <c r="I154" t="inlineStr">
         <is>
@@ -7502,7 +7502,7 @@
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/20789-truong-sinh-than-trong-lo-dich</t>
+          <t>https://sitruyencv.com/story/9529-truc-tiep-thiet-ke-tu-vong-convert</t>
         </is>
       </c>
     </row>
@@ -7514,32 +7514,32 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Tìm truyện kỳ ảo</t>
+          <t>Tìm truyện tiên hiệp hơn 500 chương</t>
         </is>
       </c>
       <c r="C155" t="n">
         <v>4</v>
       </c>
       <c r="D155" t="n">
-        <v>10142</v>
+        <v>19982</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Trở Về 84: Từ Thu Đồng Nát Bắt Đầu Làm Giàu [Convert]</t>
+          <t>Gia Tộc Tu Tiên: Ta Lấy Luân Hồi Chuyển Thế Tìm Trường Sinh [Convert]</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Đô Thị</t>
+          <t>Tiên Hiệp</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Hoàn thành</t>
+          <t>Đang ra</t>
         </is>
       </c>
       <c r="H155" t="n">
-        <v>4.8699</v>
+        <v>6.9345</v>
       </c>
       <c r="I155" t="inlineStr">
         <is>
@@ -7548,7 +7548,7 @@
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/10142-tro-ve-84-tu-thu-dong-nat-bat-dau-lam-giau-convert</t>
+          <t>https://sitruyencv.com/story/19982-gia-toc-tu-tien-ta-lay-luan-hoi-chuyen-the-tim-truong-sinh-convert</t>
         </is>
       </c>
     </row>
@@ -7560,32 +7560,32 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Tìm truyện kỳ ảo</t>
+          <t>Tìm truyện tiên hiệp hơn 500 chương</t>
         </is>
       </c>
       <c r="C156" t="n">
         <v>5</v>
       </c>
       <c r="D156" t="n">
-        <v>19317</v>
+        <v>20789</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Kinh Hồng [Dịch]</t>
+          <t>Trường sinh thận trọng lộ [Dịch]</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Tiên Hiệp, Huyền Huyễn, Lịch Sử Quân Sự, Cổ Đại, Tiên Hiệp Kỳ Duyên, Cổ Đại Ngôn Tình</t>
+          <t>Tiên Hiệp Kỳ Duyên</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Đang ra</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="H156" t="n">
-        <v>4.6272</v>
+        <v>6.1327</v>
       </c>
       <c r="I156" t="inlineStr">
         <is>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/19317-kinh-hong-dich</t>
+          <t>https://sitruyencv.com/story/20789-truong-sinh-than-trong-lo-dich</t>
         </is>
       </c>
     </row>
@@ -7606,23 +7606,23 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Tìm truyện kỳ ảo</t>
+          <t>Tìm truyện tiên hiệp hơn 500 chương</t>
         </is>
       </c>
       <c r="C157" t="n">
         <v>6</v>
       </c>
       <c r="D157" t="n">
-        <v>19505</v>
+        <v>19317</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Minh Mạt Biên Quân: Chế Tạo Hỏa Khí Tàn Sát Bát Kỳ [Convert]</t>
+          <t>Kinh Hồng [Dịch]</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Dã Sử</t>
+          <t>Tiên Hiệp, Huyền Huyễn, Lịch Sử Quân Sự, Cổ Đại, Tiên Hiệp Kỳ Duyên, Cổ Đại Ngôn Tình</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
@@ -7631,7 +7631,7 @@
         </is>
       </c>
       <c r="H157" t="n">
-        <v>4.3939</v>
+        <v>6.0723</v>
       </c>
       <c r="I157" t="inlineStr">
         <is>
@@ -7640,7 +7640,7 @@
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/19505-minh-mat-bien-quan-che-tao-hoa-khi-tan-sat-bat-ky-convert</t>
+          <t>https://sitruyencv.com/story/19317-kinh-hong-dich</t>
         </is>
       </c>
     </row>
@@ -7652,23 +7652,23 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Tìm truyện kỳ ảo</t>
+          <t>Tìm truyện tiên hiệp hơn 500 chương</t>
         </is>
       </c>
       <c r="C158" t="n">
         <v>7</v>
       </c>
       <c r="D158" t="n">
-        <v>14198</v>
+        <v>19395</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Vừa Thành Phong Hào Đấu La, Đạo Lữ Hệ Thống Tìm Tới Cửa! [Convert]</t>
+          <t>Trong Thôn Có Một Tu Tiên Tông Môn [Convert]</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Đồng Nhân</t>
+          <t>Tiên Hiệp</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
@@ -7677,7 +7677,7 @@
         </is>
       </c>
       <c r="H158" t="n">
-        <v>4.1349</v>
+        <v>5.9534</v>
       </c>
       <c r="I158" t="inlineStr">
         <is>
@@ -7686,7 +7686,7 @@
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/14198-vua-thanh-phong-hao-dau-la-dao-lu-he-thong-tim-toi-cua-convert</t>
+          <t>https://sitruyencv.com/story/19395-trong-thon-co-mot-tu-tien-tong-mon-convert</t>
         </is>
       </c>
     </row>
@@ -7698,18 +7698,18 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Tìm truyện kỳ ảo</t>
+          <t>Tìm truyện tiên hiệp hơn 500 chương</t>
         </is>
       </c>
       <c r="C159" t="n">
         <v>8</v>
       </c>
       <c r="D159" t="n">
-        <v>19982</v>
+        <v>13524</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Gia Tộc Tu Tiên: Ta Lấy Luân Hồi Chuyển Thế Tìm Trường Sinh [Convert]</t>
+          <t>Lôi Linh Căn Tu Tiên, Ta Có Gấp 10 Lần Phục Chế Không Gian [Convert]</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="H159" t="n">
-        <v>3.5961</v>
+        <v>5.5613</v>
       </c>
       <c r="I159" t="inlineStr">
         <is>
@@ -7732,7 +7732,7 @@
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/19982-gia-toc-tu-tien-ta-lay-luan-hoi-chuyen-the-tim-truong-sinh-convert</t>
+          <t>https://sitruyencv.com/story/13524-loi-linh-can-tu-tien-ta-co-gap-10-lan-phuc-che-khong-gian-convert</t>
         </is>
       </c>
     </row>
@@ -7744,32 +7744,32 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Tìm truyện kỳ ảo</t>
+          <t>Tìm truyện tiên hiệp hơn 500 chương</t>
         </is>
       </c>
       <c r="C160" t="n">
         <v>9</v>
       </c>
       <c r="D160" t="n">
-        <v>10701</v>
+        <v>20648</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Đấu La: Phong Hào Cầm Ma, Tên Sát Thủ Này Có Chút Lạnh [Convert]</t>
+          <t>Ma Tu Trọng Sinh, Mở Màn Nhặt Được Một Hành Tinh Zombie [Dịch]</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Đồng Nhân</t>
+          <t>Tiên Hiệp</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Hoàn thành</t>
+          <t>Đang ra</t>
         </is>
       </c>
       <c r="H160" t="n">
-        <v>3.5824</v>
+        <v>5.5427</v>
       </c>
       <c r="I160" t="inlineStr">
         <is>
@@ -7778,7 +7778,7 @@
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/10701-dau-la-phong-hao-cam-ma-ten-sat-thu-nay-co-chut-lanh-convert</t>
+          <t>https://sitruyencv.com/story/20648-ma-tu-trong-sinh-mo-man-nhat-duoc-mot-hanh-tinh-zombie-dich</t>
         </is>
       </c>
     </row>
@@ -7790,32 +7790,32 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Tìm truyện kỳ ảo</t>
+          <t>Tìm truyện tiên hiệp hơn 500 chương</t>
         </is>
       </c>
       <c r="C161" t="n">
         <v>10</v>
       </c>
       <c r="D161" t="n">
-        <v>20387</v>
+        <v>4828</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Nhất Kiếm Nhất Tửu Nhất Càn Khôn [Dịch]</t>
+          <t>Mắt Mù Thần Y, Bắt Đầu Gặp Được Thánh Nữ Báo Ân [Convert]</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Tiên Hiệp, Huyền Huyễn</t>
+          <t>Kiếm Hiệp</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Đang ra</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="H161" t="n">
-        <v>3.5709</v>
+        <v>5.4095</v>
       </c>
       <c r="I161" t="inlineStr">
         <is>
@@ -7824,7 +7824,7 @@
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/20387-nhat-kiem-nhat-tuu-nhat-can-khon-dich</t>
+          <t>https://sitruyencv.com/story/4828-mat-mu-than-y-bat-dau-gap-duoc-thanh-nu-bao-an-convert</t>
         </is>
       </c>
     </row>
@@ -7836,23 +7836,23 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Tìm truyện xuyên sách</t>
+          <t>Tìm truyện đô thị trạng thái đã hoàn thành</t>
         </is>
       </c>
       <c r="C162" t="n">
         <v>1</v>
       </c>
       <c r="D162" t="n">
-        <v>14198</v>
+        <v>11553</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Vừa Thành Phong Hào Đấu La, Đạo Lữ Hệ Thống Tìm Tới Cửa! [Convert]</t>
+          <t>Bắt Đầu Kém Chút Bị Ăn, May Mắn Ta Có Thể Dời Đi Mặt Trái Trạng Thái [Convert]</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Đồng Nhân</t>
+          <t>Huyền Huyễn</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
@@ -7861,7 +7861,7 @@
         </is>
       </c>
       <c r="H162" t="n">
-        <v>5.9195</v>
+        <v>11.5292</v>
       </c>
       <c r="I162" t="inlineStr">
         <is>
@@ -7870,7 +7870,7 @@
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/14198-vua-thanh-phong-hao-dau-la-dao-lu-he-thong-tim-toi-cua-convert</t>
+          <t>https://sitruyencv.com/story/11553-bat-dau-kem-chut-bi-an-may-man-ta-co-the-doi-di-mat-trai-trang-thai-convert</t>
         </is>
       </c>
     </row>
@@ -7882,23 +7882,23 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Tìm truyện xuyên sách</t>
+          <t>Tìm truyện đô thị trạng thái đã hoàn thành</t>
         </is>
       </c>
       <c r="C163" t="n">
         <v>2</v>
       </c>
       <c r="D163" t="n">
-        <v>20479</v>
+        <v>16102</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Ta, Konoha Thôn Đệ Nhất Ác Tặc [Dịch]</t>
+          <t>Diễn Kẻ Nghiện Giống Như Thật ? Tra Hắn [Convert]</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Đồng Nhân, Hệ Thống, Xuyên Sách</t>
+          <t>Đô Thị</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
@@ -7907,7 +7907,7 @@
         </is>
       </c>
       <c r="H163" t="n">
-        <v>5.9192</v>
+        <v>9.756</v>
       </c>
       <c r="I163" t="inlineStr">
         <is>
@@ -7916,7 +7916,7 @@
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/20479-ta-konoha-thon-de-nhat-ac-tac-dich</t>
+          <t>https://sitruyencv.com/story/16102-dien-ke-nghien-giong-nhu-that-tra-han-convert</t>
         </is>
       </c>
     </row>
@@ -7928,32 +7928,32 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Tìm truyện xuyên sách</t>
+          <t>Tìm truyện đô thị trạng thái đã hoàn thành</t>
         </is>
       </c>
       <c r="C164" t="n">
         <v>3</v>
       </c>
       <c r="D164" t="n">
-        <v>20532</v>
+        <v>19530</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Vai Ác: Bắt Đầu Đánh Mặt Chiến Thần, Nữ Tổng Giám Đốc Giúp Ta Xuất Khí [Dịch]</t>
+          <t>Cái Gì?! Giấy Nháp Của Ta Trở Thành Cơ Mật Quốc Gia Rồi [Convert]</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Đô Thị, Hệ Thống, Xuyên Sách</t>
+          <t>Đô Thị</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Hoàn thành</t>
+          <t>Tạm dừng</t>
         </is>
       </c>
       <c r="H164" t="n">
-        <v>5.67</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="I164" t="inlineStr">
         <is>
@@ -7962,7 +7962,7 @@
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/20532-vai-ac-bat-dau-danh-mat-chien-than-nu-tong-giam-doc-giup-ta-xuat-khi-dich</t>
+          <t>https://sitruyencv.com/story/19530-cai-gi-giay-nhap-cua-ta-tro-thanh-co-mat-quoc-gia-roi-convert</t>
         </is>
       </c>
     </row>
@@ -7974,23 +7974,23 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Tìm truyện xuyên sách</t>
+          <t>Tìm truyện đô thị trạng thái đã hoàn thành</t>
         </is>
       </c>
       <c r="C165" t="n">
         <v>4</v>
       </c>
       <c r="D165" t="n">
-        <v>17792</v>
+        <v>16928</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Ta Câu Thông Tương Lai, Giết Xuyên Tận Thế Này! [Convert]</t>
+          <t>Nơi Ẩn Núp Thuyết Tiến Hoá [Convert]</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Huyền Nghi</t>
+          <t>Đô Thị</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
@@ -7999,7 +7999,7 @@
         </is>
       </c>
       <c r="H165" t="n">
-        <v>5.6166</v>
+        <v>9.147600000000001</v>
       </c>
       <c r="I165" t="inlineStr">
         <is>
@@ -8008,7 +8008,7 @@
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/17792-ta-cau-thong-tuong-lai-giet-xuyen-tan-the-nay-convert</t>
+          <t>https://sitruyencv.com/story/16928-noi-an-nup-thuyet-tien-hoa-convert</t>
         </is>
       </c>
     </row>
@@ -8020,32 +8020,32 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Tìm truyện xuyên sách</t>
+          <t>Tìm truyện đô thị trạng thái đã hoàn thành</t>
         </is>
       </c>
       <c r="C166" t="n">
         <v>5</v>
       </c>
       <c r="D166" t="n">
-        <v>18457</v>
+        <v>14998</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Thiên Băng Khai Cục, Từ Tử Tù Doanh Chém Tới Chiến Vương [Dịch]</t>
+          <t>Cao Khảo Sau Đó, Ta Lại Bị Quốc Gia Sss Cấp Mã Hóa [Convert]</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Hệ Thống, Lịch Sử Quân Sự, Xuyên Sách</t>
+          <t>Đô Thị</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Đang ra</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="H166" t="n">
-        <v>5.4265</v>
+        <v>8.5145</v>
       </c>
       <c r="I166" t="inlineStr">
         <is>
@@ -8054,7 +8054,7 @@
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/18457-thien-bang-khai-cuc-tu-tu-tu-doanh-chem-toi-chien-vuong-dich</t>
+          <t>https://sitruyencv.com/story/14998-cao-khao-sau-do-ta-lai-bi-quoc-gia-sss-cap-ma-hoa-convert</t>
         </is>
       </c>
     </row>
@@ -8066,32 +8066,32 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Tìm truyện xuyên sách</t>
+          <t>Tìm truyện đô thị trạng thái đã hoàn thành</t>
         </is>
       </c>
       <c r="C167" t="n">
         <v>6</v>
       </c>
       <c r="D167" t="n">
-        <v>8416</v>
+        <v>17914</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>70 Ta Thành Nữ Chủ Cực Phẩm Tam Tẩu [Convert]</t>
+          <t>Không Có Tiền Về Nhà Ăn Tết? Phát Cái Hồng Bao Vạn Lần Hoàn Lại [Convert]</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Hiện Đại Ngôn Tình</t>
+          <t>Đô Thị</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Hoàn thành</t>
+          <t>Đang ra</t>
         </is>
       </c>
       <c r="H167" t="n">
-        <v>5.2909</v>
+        <v>8.4976</v>
       </c>
       <c r="I167" t="inlineStr">
         <is>
@@ -8100,7 +8100,7 @@
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/8416-70-ta-thanh-nu-chu-cuc-pham-tam-tau-convert</t>
+          <t>https://sitruyencv.com/story/17914-khong-co-tien-ve-nha-an-tet-phat-cai-hong-bao-van-lan-hoan-lai-convert</t>
         </is>
       </c>
     </row>
@@ -8112,23 +8112,23 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Tìm truyện xuyên sách</t>
+          <t>Tìm truyện đô thị trạng thái đã hoàn thành</t>
         </is>
       </c>
       <c r="C168" t="n">
         <v>7</v>
       </c>
       <c r="D168" t="n">
-        <v>12265</v>
+        <v>19111</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Đại Nương Tử Chỉ Muốn Nằm Thẳng [Convert]</t>
+          <t>Người Ở Tu Tiên Giới, Lại Cho Ta Hệ Thống Đô Thị Thần Hào? [Convert]</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Cổ Đại Ngôn Tình</t>
+          <t>Tiên Hiệp</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="H168" t="n">
-        <v>5.0718</v>
+        <v>8.4443</v>
       </c>
       <c r="I168" t="inlineStr">
         <is>
@@ -8146,7 +8146,7 @@
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/12265-dai-nuong-tu-chi-muon-nam-thang-convert</t>
+          <t>https://sitruyencv.com/story/19111-nguoi-o-tu-tien-gioi-lai-cho-ta-he-thong-do-thi-than-hao-convert</t>
         </is>
       </c>
     </row>
@@ -8158,32 +8158,32 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Tìm truyện xuyên sách</t>
+          <t>Tìm truyện đô thị trạng thái đã hoàn thành</t>
         </is>
       </c>
       <c r="C169" t="n">
         <v>8</v>
       </c>
       <c r="D169" t="n">
-        <v>8524</v>
+        <v>17972</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Mạt Thế Trọng Sinh: Tuyệt Sắc Pháo Hôi Đại Tiểu Thư Nghịch Tập [Convert]</t>
+          <t>Ai Đem Địa Phủ Câu Hồn Làm Kéo Vào Quỷ Dị Phó Bản? [Convert]</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Hiện Đại Ngôn Tình</t>
+          <t>Huyền Nghi</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Hoàn thành</t>
+          <t>Đang ra</t>
         </is>
       </c>
       <c r="H169" t="n">
-        <v>4.9807</v>
+        <v>8.1229</v>
       </c>
       <c r="I169" t="inlineStr">
         <is>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/8524-mat-the-trong-sinh-tuyet-sac-phao-hoi-dai-tieu-thu-nghich-tap-convert</t>
+          <t>https://sitruyencv.com/story/17972-ai-dem-dia-phu-cau-hon-lam-keo-vao-quy-di-pho-ban-convert</t>
         </is>
       </c>
     </row>
@@ -8204,23 +8204,23 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Tìm truyện xuyên sách</t>
+          <t>Tìm truyện đô thị trạng thái đã hoàn thành</t>
         </is>
       </c>
       <c r="C170" t="n">
         <v>9</v>
       </c>
       <c r="D170" t="n">
-        <v>19982</v>
+        <v>12674</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Gia Tộc Tu Tiên: Ta Lấy Luân Hồi Chuyển Thế Tìm Trường Sinh [Convert]</t>
+          <t>Quá Tốt Rồi, Là Biến Thái Hàng Xóm, Chúng Ta Không Cứu Nổi [Convert]</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Tiên Hiệp</t>
+          <t>Đô Thị</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
@@ -8229,7 +8229,7 @@
         </is>
       </c>
       <c r="H170" t="n">
-        <v>4.6558</v>
+        <v>8.1183</v>
       </c>
       <c r="I170" t="inlineStr">
         <is>
@@ -8238,7 +8238,7 @@
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/19982-gia-toc-tu-tien-ta-lay-luan-hoi-chuyen-the-tim-truong-sinh-convert</t>
+          <t>https://sitruyencv.com/story/12674-qua-tot-roi-la-bien-thai-hang-xom-chung-ta-khong-cuu-noi-convert</t>
         </is>
       </c>
     </row>
@@ -8250,32 +8250,32 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Tìm truyện xuyên sách</t>
+          <t>Tìm truyện đô thị trạng thái đã hoàn thành</t>
         </is>
       </c>
       <c r="C171" t="n">
         <v>10</v>
       </c>
       <c r="D171" t="n">
-        <v>20025</v>
+        <v>20392</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Phàm Nhân Tu Tiên: Kim Thủ Chỉ Của Ta Lại Là Một Quyển Sách [Convert]</t>
+          <t>Nhà Ta Thế Hệ Cường Đạo, Tiểu Tử Ngươi Thi Đậu Trạng Nguyên [Dịch]</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Tiên Hiệp</t>
+          <t>Huyền Huyễn, Cổ Đại</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Đang ra</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="H171" t="n">
-        <v>4.4409</v>
+        <v>8.0566</v>
       </c>
       <c r="I171" t="inlineStr">
         <is>
@@ -8284,7 +8284,7 @@
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/20025-pham-nhan-tu-tien-kim-thu-chi-cua-ta-lai-la-mot-quyen-sach-convert</t>
+          <t>https://sitruyencv.com/story/20392-nha-ta-the-he-cuong-dao-tieu-tu-nguoi-thi-dau-trang-nguyen-dich</t>
         </is>
       </c>
     </row>
@@ -8296,32 +8296,32 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Tìm truyện hiện đại ngôn tình</t>
+          <t>Tìm truyện hiện đại ngôn tình trạng thái đang ra</t>
         </is>
       </c>
       <c r="C172" t="n">
         <v>1</v>
       </c>
       <c r="D172" t="n">
-        <v>8979</v>
+        <v>12568</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>70 Quân Hôn Binh Vương Đầu Quả Tim Sủng [Convert]</t>
+          <t>Phượng Trì Sinh Xuân [Convert]</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Hiện Đại Ngôn Tình</t>
+          <t>Cổ Đại Ngôn Tình</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Hoàn thành</t>
+          <t>Đang ra</t>
         </is>
       </c>
       <c r="H172" t="n">
-        <v>12.4743</v>
+        <v>13.1141</v>
       </c>
       <c r="I172" t="inlineStr">
         <is>
@@ -8330,7 +8330,7 @@
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/8979-70-quan-hon-binh-vuong-dau-qua-tim-sung-convert</t>
+          <t>https://sitruyencv.com/story/12568-phuong-tri-sinh-xuan-convert</t>
         </is>
       </c>
     </row>
@@ -8342,18 +8342,18 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Tìm truyện hiện đại ngôn tình</t>
+          <t>Tìm truyện hiện đại ngôn tình trạng thái đang ra</t>
         </is>
       </c>
       <c r="C173" t="n">
         <v>2</v>
       </c>
       <c r="D173" t="n">
-        <v>8524</v>
+        <v>8979</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Mạt Thế Trọng Sinh: Tuyệt Sắc Pháo Hôi Đại Tiểu Thư Nghịch Tập [Convert]</t>
+          <t>70 Quân Hôn Binh Vương Đầu Quả Tim Sủng [Convert]</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -8367,7 +8367,7 @@
         </is>
       </c>
       <c r="H173" t="n">
-        <v>12.3969</v>
+        <v>12.4743</v>
       </c>
       <c r="I173" t="inlineStr">
         <is>
@@ -8376,7 +8376,7 @@
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/8524-mat-the-trong-sinh-tuyet-sac-phao-hoi-dai-tieu-thu-nghich-tap-convert</t>
+          <t>https://sitruyencv.com/story/8979-70-quan-hon-binh-vuong-dau-qua-tim-sung-convert</t>
         </is>
       </c>
     </row>
@@ -8388,23 +8388,23 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Tìm truyện hiện đại ngôn tình</t>
+          <t>Tìm truyện hiện đại ngôn tình trạng thái đang ra</t>
         </is>
       </c>
       <c r="C174" t="n">
         <v>3</v>
       </c>
       <c r="D174" t="n">
-        <v>18381</v>
+        <v>8524</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Trùng Sinh Quan Vận Hanh Thông [Dịch]</t>
+          <t>Mạt Thế Trọng Sinh: Tuyệt Sắc Pháo Hôi Đại Tiểu Thư Nghịch Tập [Convert]</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Đô Thị, Trinh Thám, Hiện Đại Ngôn Tình</t>
+          <t>Hiện Đại Ngôn Tình</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
@@ -8413,7 +8413,7 @@
         </is>
       </c>
       <c r="H174" t="n">
-        <v>12.1454</v>
+        <v>12.3969</v>
       </c>
       <c r="I174" t="inlineStr">
         <is>
@@ -8422,7 +8422,7 @@
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/18381-trung-sinh-quan-van-hanh-thong-dich</t>
+          <t>https://sitruyencv.com/story/8524-mat-the-trong-sinh-tuyet-sac-phao-hoi-dai-tieu-thu-nghich-tap-convert</t>
         </is>
       </c>
     </row>
@@ -8434,23 +8434,23 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Tìm truyện hiện đại ngôn tình</t>
+          <t>Tìm truyện hiện đại ngôn tình trạng thái đang ra</t>
         </is>
       </c>
       <c r="C175" t="n">
         <v>4</v>
       </c>
       <c r="D175" t="n">
-        <v>19317</v>
+        <v>11553</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Kinh Hồng [Dịch]</t>
+          <t>Bắt Đầu Kém Chút Bị Ăn, May Mắn Ta Có Thể Dời Đi Mặt Trái Trạng Thái [Convert]</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Tiên Hiệp, Huyền Huyễn, Lịch Sử Quân Sự, Cổ Đại, Tiên Hiệp Kỳ Duyên, Cổ Đại Ngôn Tình</t>
+          <t>Huyền Huyễn</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="H175" t="n">
-        <v>11.9679</v>
+        <v>12.2126</v>
       </c>
       <c r="I175" t="inlineStr">
         <is>
@@ -8468,7 +8468,7 @@
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/19317-kinh-hong-dich</t>
+          <t>https://sitruyencv.com/story/11553-bat-dau-kem-chut-bi-an-may-man-ta-co-the-doi-di-mat-trai-trang-thai-convert</t>
         </is>
       </c>
     </row>
@@ -8480,23 +8480,23 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Tìm truyện hiện đại ngôn tình</t>
+          <t>Tìm truyện hiện đại ngôn tình trạng thái đang ra</t>
         </is>
       </c>
       <c r="C176" t="n">
         <v>5</v>
       </c>
       <c r="D176" t="n">
-        <v>8416</v>
+        <v>18381</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>70 Ta Thành Nữ Chủ Cực Phẩm Tam Tẩu [Convert]</t>
+          <t>Trùng Sinh Quan Vận Hanh Thông [Dịch]</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Hiện Đại Ngôn Tình</t>
+          <t>Đô Thị, Trinh Thám, Hiện Đại Ngôn Tình</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
@@ -8505,7 +8505,7 @@
         </is>
       </c>
       <c r="H176" t="n">
-        <v>11.8547</v>
+        <v>12.1454</v>
       </c>
       <c r="I176" t="inlineStr">
         <is>
@@ -8514,7 +8514,7 @@
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/8416-70-ta-thanh-nu-chu-cuc-pham-tam-tau-convert</t>
+          <t>https://sitruyencv.com/story/18381-trung-sinh-quan-van-hanh-thong-dich</t>
         </is>
       </c>
     </row>
@@ -8526,23 +8526,23 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Tìm truyện hiện đại ngôn tình</t>
+          <t>Tìm truyện hiện đại ngôn tình trạng thái đang ra</t>
         </is>
       </c>
       <c r="C177" t="n">
         <v>6</v>
       </c>
       <c r="D177" t="n">
-        <v>12265</v>
+        <v>19317</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Đại Nương Tử Chỉ Muốn Nằm Thẳng [Convert]</t>
+          <t>Kinh Hồng [Dịch]</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Cổ Đại Ngôn Tình</t>
+          <t>Tiên Hiệp, Huyền Huyễn, Lịch Sử Quân Sự, Cổ Đại, Tiên Hiệp Kỳ Duyên, Cổ Đại Ngôn Tình</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
@@ -8551,7 +8551,7 @@
         </is>
       </c>
       <c r="H177" t="n">
-        <v>11.5001</v>
+        <v>11.9679</v>
       </c>
       <c r="I177" t="inlineStr">
         <is>
@@ -8560,7 +8560,7 @@
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/12265-dai-nuong-tu-chi-muon-nam-thang-convert</t>
+          <t>https://sitruyencv.com/story/19317-kinh-hong-dich</t>
         </is>
       </c>
     </row>
@@ -8572,18 +8572,18 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Tìm truyện hiện đại ngôn tình</t>
+          <t>Tìm truyện hiện đại ngôn tình trạng thái đang ra</t>
         </is>
       </c>
       <c r="C178" t="n">
         <v>7</v>
       </c>
       <c r="D178" t="n">
-        <v>12188</v>
+        <v>8416</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Thiên Tai Tận Thế, Nàng Trữ Đầy Vật Tư Phía Sau Giết Điên Rồi [Convert]</t>
+          <t>70 Ta Thành Nữ Chủ Cực Phẩm Tam Tẩu [Convert]</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -8593,11 +8593,11 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Đang ra</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="H178" t="n">
-        <v>11.1147</v>
+        <v>11.8547</v>
       </c>
       <c r="I178" t="inlineStr">
         <is>
@@ -8606,7 +8606,7 @@
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/12188-thien-tai-tan-the-nang-tru-day-vat-tu-phia-sau-giet-dien-roi-convert</t>
+          <t>https://sitruyencv.com/story/8416-70-ta-thanh-nu-chu-cuc-pham-tam-tau-convert</t>
         </is>
       </c>
     </row>
@@ -8618,32 +8618,32 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Tìm truyện hiện đại ngôn tình</t>
+          <t>Tìm truyện hiện đại ngôn tình trạng thái đang ra</t>
         </is>
       </c>
       <c r="C179" t="n">
         <v>8</v>
       </c>
       <c r="D179" t="n">
-        <v>20043</v>
+        <v>12265</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Giải Trí: Cùng Các Minh Tinh Sin Tồn Trên Hoang Đảo [Dịch]</t>
+          <t>Đại Nương Tử Chỉ Muốn Nằm Thẳng [Convert]</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Đô Thị, Kỳ Ảo, Hệ Thống, Tây Phương Kỳ Huyễn, Biến Thân, Điền Văn, Ngôn Tình, Nữ Phụ, Hiện Đại Ngôn Tình, Lãng Mạn Thanh Xuân</t>
+          <t>Cổ Đại Ngôn Tình</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Hoàn thành</t>
+          <t>Đang ra</t>
         </is>
       </c>
       <c r="H179" t="n">
-        <v>10.2858</v>
+        <v>11.5001</v>
       </c>
       <c r="I179" t="inlineStr">
         <is>
@@ -8652,7 +8652,7 @@
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/20043-giai-tri-cung-cac-minh-tinh-sin-ton-tren-hoang-dao-dich</t>
+          <t>https://sitruyencv.com/story/12265-dai-nuong-tu-chi-muon-nam-thang-convert</t>
         </is>
       </c>
     </row>
@@ -8664,32 +8664,32 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Tìm truyện hiện đại ngôn tình</t>
+          <t>Tìm truyện hiện đại ngôn tình trạng thái đang ra</t>
         </is>
       </c>
       <c r="C180" t="n">
         <v>9</v>
       </c>
       <c r="D180" t="n">
-        <v>2021</v>
+        <v>12188</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Dựa Vào Làm Ruộng Đi Lên Đỉnh Cao Nhân Sinh [Convert]</t>
+          <t>Thiên Tai Tận Thế, Nàng Trữ Đầy Vật Tư Phía Sau Giết Điên Rồi [Convert]</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Cổ Đại Ngôn Tình</t>
+          <t>Hiện Đại Ngôn Tình</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Hoàn thành</t>
+          <t>Đang ra</t>
         </is>
       </c>
       <c r="H180" t="n">
-        <v>10.0495</v>
+        <v>11.1147</v>
       </c>
       <c r="I180" t="inlineStr">
         <is>
@@ -8698,7 +8698,7 @@
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/2021-dua-vao-lam-ruong-di-len-dinh-cao-nhan-sinh-convert</t>
+          <t>https://sitruyencv.com/story/12188-thien-tai-tan-the-nang-tru-day-vat-tu-phia-sau-giet-dien-roi-convert</t>
         </is>
       </c>
     </row>
@@ -8710,32 +8710,32 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Tìm truyện hiện đại ngôn tình</t>
+          <t>Tìm truyện hiện đại ngôn tình trạng thái đang ra</t>
         </is>
       </c>
       <c r="C181" t="n">
         <v>10</v>
       </c>
       <c r="D181" t="n">
-        <v>19064</v>
+        <v>20043</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Hợp Hoan Tông, Từ Chăm Sóc Đạo Lữ Của Sư Đệ Bắt Đầu Tu Tiên [Dịch]</t>
+          <t>Giải Trí: Cùng Các Minh Tinh Sin Tồn Trên Hoang Đảo [Dịch]</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Huyền Huyễn, Hệ Thống, Phản Phái, Cổ Đại, Tiên Hiệp Kỳ Duyên, Cổ Đại Ngôn Tình</t>
+          <t>Đô Thị, Kỳ Ảo, Hệ Thống, Tây Phương Kỳ Huyễn, Biến Thân, Điền Văn, Ngôn Tình, Nữ Phụ, Hiện Đại Ngôn Tình, Lãng Mạn Thanh Xuân</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Đang ra</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="H181" t="n">
-        <v>9.879799999999999</v>
+        <v>10.8426</v>
       </c>
       <c r="I181" t="inlineStr">
         <is>
@@ -8744,7 +8744,7 @@
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/19064-hop-hoan-tong-tu-cham-soc-dao-lu-cua-su-de-bat-dau-tu-tien-dich</t>
+          <t>https://sitruyencv.com/story/20043-giai-tri-cung-cac-minh-tinh-sin-ton-tren-hoang-dao-dich</t>
         </is>
       </c>
     </row>
@@ -8756,7 +8756,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Tìm truyện tây phương kỳ huyễn</t>
+          <t>Tìm truyện tây phương kỳ huyễn ít hơn 200 chương</t>
         </is>
       </c>
       <c r="C182" t="n">
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="H182" t="n">
-        <v>10.0832</v>
+        <v>15.0447</v>
       </c>
       <c r="I182" t="inlineStr">
         <is>
@@ -8802,23 +8802,23 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Tìm truyện tây phương kỳ huyễn</t>
+          <t>Tìm truyện tây phương kỳ huyễn ít hơn 200 chương</t>
         </is>
       </c>
       <c r="C183" t="n">
         <v>2</v>
       </c>
       <c r="D183" t="n">
-        <v>20293</v>
+        <v>20043</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Ngục Giam Tế Bào Của Ta [Dịch]</t>
+          <t>Giải Trí: Cùng Các Minh Tinh Sin Tồn Trên Hoang Đảo [Dịch]</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Khoa Huyễn, Kỳ Ảo, Tây Phương Kỳ Huyễn, Dị Giới, Khoa Huyễn Không Gian</t>
+          <t>Đô Thị, Kỳ Ảo, Hệ Thống, Tây Phương Kỳ Huyễn, Biến Thân, Điền Văn, Ngôn Tình, Nữ Phụ, Hiện Đại Ngôn Tình, Lãng Mạn Thanh Xuân</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
@@ -8827,7 +8827,7 @@
         </is>
       </c>
       <c r="H183" t="n">
-        <v>10.0099</v>
+        <v>11.0634</v>
       </c>
       <c r="I183" t="inlineStr">
         <is>
@@ -8836,7 +8836,7 @@
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/20293-nguc-giam-te-bao-cua-ta-dich</t>
+          <t>https://sitruyencv.com/story/20043-giai-tri-cung-cac-minh-tinh-sin-ton-tren-hoang-dao-dich</t>
         </is>
       </c>
     </row>
@@ -8848,23 +8848,23 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Tìm truyện tây phương kỳ huyễn</t>
+          <t>Tìm truyện tây phương kỳ huyễn ít hơn 200 chương</t>
         </is>
       </c>
       <c r="C184" t="n">
         <v>3</v>
       </c>
       <c r="D184" t="n">
-        <v>19282</v>
+        <v>20293</v>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Những Ngày Sinh Sống Tại Hogwarts [Convert]</t>
+          <t>Ngục Giam Tế Bào Của Ta [Dịch]</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Đồng Nhân, Tây Phương Kỳ Huyễn, Thanh Xuân Vườn Trường, Hiện Đại Ngôn Tình, Lãng Mạn Thanh Xuân</t>
+          <t>Khoa Huyễn, Kỳ Ảo, Tây Phương Kỳ Huyễn, Dị Giới, Khoa Huyễn Không Gian</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
@@ -8873,7 +8873,7 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>9.5345</v>
+        <v>10.0099</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -8882,7 +8882,7 @@
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/19282-nhung-ngay-sinh-song-tai-hogwarts-convert</t>
+          <t>https://sitruyencv.com/story/20293-nguc-giam-te-bao-cua-ta-dich</t>
         </is>
       </c>
     </row>
@@ -8894,23 +8894,23 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Tìm truyện tây phương kỳ huyễn</t>
+          <t>Tìm truyện tây phương kỳ huyễn ít hơn 200 chương</t>
         </is>
       </c>
       <c r="C185" t="n">
         <v>4</v>
       </c>
       <c r="D185" t="n">
-        <v>20576</v>
+        <v>19282</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Đấu La: Thiên Cổ Nhất Đế, Khởi Đầu Triệu Hoán Đại Tuyết Long Kỵ [Dịch]</t>
+          <t>Những Ngày Sinh Sống Tại Hogwarts [Convert]</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Huyền Huyễn, Đồng Nhân, Tây Phương Kỳ Huyễn</t>
+          <t>Đồng Nhân, Tây Phương Kỳ Huyễn, Thanh Xuân Vườn Trường, Hiện Đại Ngôn Tình, Lãng Mạn Thanh Xuân</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
@@ -8919,7 +8919,7 @@
         </is>
       </c>
       <c r="H185" t="n">
-        <v>8.9748</v>
+        <v>9.5345</v>
       </c>
       <c r="I185" t="inlineStr">
         <is>
@@ -8928,7 +8928,7 @@
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/20576-dau-la-thien-co-nhat-de-khoi-dau-trieu-hoan-dai-tuyet-long-ky-dich</t>
+          <t>https://sitruyencv.com/story/19282-nhung-ngay-sinh-song-tai-hogwarts-convert</t>
         </is>
       </c>
     </row>
@@ -8940,32 +8940,32 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Tìm truyện tây phương kỳ huyễn</t>
+          <t>Tìm truyện tây phương kỳ huyễn ít hơn 200 chương</t>
         </is>
       </c>
       <c r="C186" t="n">
         <v>5</v>
       </c>
       <c r="D186" t="n">
-        <v>18454</v>
+        <v>20576</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Vô Tận Hàn Đông: Doanh Địa Của Ta Thăng Cấp Vô Hạn [Dịch]</t>
+          <t>Đấu La: Thiên Cổ Nhất Đế, Khởi Đầu Triệu Hoán Đại Tuyết Long Kỵ [Dịch]</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Hệ Thống, Tây Phương Kỳ Huyễn, Xuyên Sách, Dị Giới, Dị Năng, Mạt Thế</t>
+          <t>Huyền Huyễn, Đồng Nhân, Tây Phương Kỳ Huyễn</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Đang ra</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="H186" t="n">
-        <v>8.7593</v>
+        <v>8.9748</v>
       </c>
       <c r="I186" t="inlineStr">
         <is>
@@ -8974,7 +8974,7 @@
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/18454-vo-tan-han-dong-doanh-dia-cua-ta-thang-cap-vo-han-dich</t>
+          <t>https://sitruyencv.com/story/20576-dau-la-thien-co-nhat-de-khoi-dau-trieu-hoan-dai-tuyet-long-ky-dich</t>
         </is>
       </c>
     </row>
@@ -8986,23 +8986,23 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Tìm truyện tây phương kỳ huyễn</t>
+          <t>Tìm truyện tây phương kỳ huyễn ít hơn 200 chương</t>
         </is>
       </c>
       <c r="C187" t="n">
         <v>6</v>
       </c>
       <c r="D187" t="n">
-        <v>17831</v>
+        <v>18454</v>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Ta Thật Muốn Khống Chế Ngươi, Hoàng Nữ Điện Hạ [Convert]</t>
+          <t>Vô Tận Hàn Đông: Doanh Địa Của Ta Thăng Cấp Vô Hạn [Dịch]</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Kỳ Ảo</t>
+          <t>Hệ Thống, Tây Phương Kỳ Huyễn, Xuyên Sách, Dị Giới, Dị Năng, Mạt Thế</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
@@ -9011,7 +9011,7 @@
         </is>
       </c>
       <c r="H187" t="n">
-        <v>8.586399999999999</v>
+        <v>8.7593</v>
       </c>
       <c r="I187" t="inlineStr">
         <is>
@@ -9020,7 +9020,7 @@
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/17831-ta-that-muon-khong-che-nguoi-hoang-nu-dien-ha-convert</t>
+          <t>https://sitruyencv.com/story/18454-vo-tan-han-dong-doanh-dia-cua-ta-thang-cap-vo-han-dich</t>
         </is>
       </c>
     </row>
@@ -9032,32 +9032,32 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Tìm truyện tây phương kỳ huyễn</t>
+          <t>Tìm truyện tây phương kỳ huyễn ít hơn 200 chương</t>
         </is>
       </c>
       <c r="C188" t="n">
         <v>7</v>
       </c>
       <c r="D188" t="n">
-        <v>20799</v>
+        <v>17831</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Ta Là Đạo Sĩ Mao Sơn, Sao Toàn Là Tà Thuật [Dịch]</t>
+          <t>Ta Thật Muốn Khống Chế Ngươi, Hoàng Nữ Điện Hạ [Convert]</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Đô Thị, Huyền Huyễn, Kỳ Ảo, Tây Phương Kỳ Huyễn, Linh Dị, Huyền Nghi Thần Quái, Lãng Mạn Thanh Xuân</t>
+          <t>Kỳ Ảo</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Hoàn thành</t>
+          <t>Đang ra</t>
         </is>
       </c>
       <c r="H188" t="n">
-        <v>8.5283</v>
+        <v>8.586399999999999</v>
       </c>
       <c r="I188" t="inlineStr">
         <is>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/20799-ta-la-dao-si-mao-son-sao-toan-la-ta-thuat-dich</t>
+          <t>https://sitruyencv.com/story/17831-ta-that-muon-khong-che-nguoi-hoang-nu-dien-ha-convert</t>
         </is>
       </c>
     </row>
@@ -9078,23 +9078,23 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Tìm truyện tây phương kỳ huyễn</t>
+          <t>Tìm truyện tây phương kỳ huyễn ít hơn 200 chương</t>
         </is>
       </c>
       <c r="C189" t="n">
         <v>8</v>
       </c>
       <c r="D189" t="n">
-        <v>20043</v>
+        <v>20799</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Giải Trí: Cùng Các Minh Tinh Sin Tồn Trên Hoang Đảo [Dịch]</t>
+          <t>Ta Là Đạo Sĩ Mao Sơn, Sao Toàn Là Tà Thuật [Dịch]</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Đô Thị, Kỳ Ảo, Hệ Thống, Tây Phương Kỳ Huyễn, Biến Thân, Điền Văn, Ngôn Tình, Nữ Phụ, Hiện Đại Ngôn Tình, Lãng Mạn Thanh Xuân</t>
+          <t>Đô Thị, Huyền Huyễn, Kỳ Ảo, Tây Phương Kỳ Huyễn, Linh Dị, Huyền Nghi Thần Quái, Lãng Mạn Thanh Xuân</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="H189" t="n">
-        <v>8.4312</v>
+        <v>8.5283</v>
       </c>
       <c r="I189" t="inlineStr">
         <is>
@@ -9112,7 +9112,7 @@
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/20043-giai-tri-cung-cac-minh-tinh-sin-ton-tren-hoang-dao-dich</t>
+          <t>https://sitruyencv.com/story/20799-ta-la-dao-si-mao-son-sao-toan-la-ta-thuat-dich</t>
         </is>
       </c>
     </row>
@@ -9124,7 +9124,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Tìm truyện tây phương kỳ huyễn</t>
+          <t>Tìm truyện tây phương kỳ huyễn ít hơn 200 chương</t>
         </is>
       </c>
       <c r="C190" t="n">
@@ -9170,32 +9170,32 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Tìm truyện tây phương kỳ huyễn</t>
+          <t>Tìm truyện tây phương kỳ huyễn ít hơn 200 chương</t>
         </is>
       </c>
       <c r="C191" t="n">
         <v>10</v>
       </c>
       <c r="D191" t="n">
-        <v>3074</v>
+        <v>9529</v>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Trộm Mộ: Bắt Đầu Triệu Hoán Bất Lương Soái, Nộ Tình Tương Tây [Convert]</t>
+          <t>Trực Tiếp Thiết Kế Tử Vong [Convert]</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Huyền Huyễn</t>
+          <t>Đô Thị</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Đang ra</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="H191" t="n">
-        <v>6.847</v>
+        <v>7.3699</v>
       </c>
       <c r="I191" t="inlineStr">
         <is>
@@ -9204,7 +9204,7 @@
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/3074-trom-mo-bat-dau-trieu-hoan-bat-luong-soai-no-tinh-tuong-tay-convert</t>
+          <t>https://sitruyencv.com/story/9529-truc-tiep-thiet-ke-tu-vong-convert</t>
         </is>
       </c>
     </row>
@@ -17036,7 +17036,7 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>Tìm truyện có bối cảnh dị thế đại lục</t>
+          <t>Tìm truyện có bối cảnh dị thế đại lục, trang thái truyện đã hoàn thành</t>
         </is>
       </c>
       <c r="C362" t="n">
@@ -17061,7 +17061,7 @@
         </is>
       </c>
       <c r="H362" t="n">
-        <v>13.8699</v>
+        <v>16.4286</v>
       </c>
       <c r="I362" t="inlineStr">
         <is>
@@ -17082,23 +17082,23 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Tìm truyện có bối cảnh dị thế đại lục</t>
+          <t>Tìm truyện có bối cảnh dị thế đại lục, trang thái truyện đã hoàn thành</t>
         </is>
       </c>
       <c r="C363" t="n">
         <v>2</v>
       </c>
       <c r="D363" t="n">
-        <v>18853</v>
+        <v>12820</v>
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>Tây Du: Bắt Đầu Từ Công Chiếu Đại Thoại Tây Du [Dịch]</t>
+          <t>Đấu La: Ta, Cử Thế Tiên Sư, Thu Đồ Ninh Vinh Vinh [Convert]</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>Tiên Hiệp, Huyền Huyễn, Đồng Nhân, Hệ Thống</t>
+          <t>Đồng Nhân</t>
         </is>
       </c>
       <c r="G363" t="inlineStr">
@@ -17107,7 +17107,7 @@
         </is>
       </c>
       <c r="H363" t="n">
-        <v>11.8284</v>
+        <v>12.5754</v>
       </c>
       <c r="I363" t="inlineStr">
         <is>
@@ -17116,7 +17116,7 @@
       </c>
       <c r="J363" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/18853-tay-du-bat-dau-tu-cong-chieu-dai-thoai-tay-du-dich</t>
+          <t>https://sitruyencv.com/story/12820-dau-la-ta-cu-the-tien-su-thu-do-ninh-vinh-vinh-convert</t>
         </is>
       </c>
     </row>
@@ -17128,32 +17128,32 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Tìm truyện có bối cảnh dị thế đại lục</t>
+          <t>Tìm truyện có bối cảnh dị thế đại lục, trang thái truyện đã hoàn thành</t>
         </is>
       </c>
       <c r="C364" t="n">
         <v>3</v>
       </c>
       <c r="D364" t="n">
-        <v>18831</v>
+        <v>5138</v>
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>Hệ Thống Trừu Tượng, Ta Cũng Chẳng Kém Gì!!! [Dịch]</t>
+          <t>Đánh Dấu Già Thiên Trăm Năm Thành Thánh [Convert]</t>
         </is>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>Đô Thị, Hệ Thống</t>
+          <t>Huyền Huyễn</t>
         </is>
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>Đang ra</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="H364" t="n">
-        <v>10.7534</v>
+        <v>12.4509</v>
       </c>
       <c r="I364" t="inlineStr">
         <is>
@@ -17162,7 +17162,7 @@
       </c>
       <c r="J364" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/18831-he-thong-truu-tuong-ta-cung-chang-kem-gi-dich</t>
+          <t>https://sitruyencv.com/story/5138-danh-dau-gia-thien-tram-nam-thanh-thanh-convert</t>
         </is>
       </c>
     </row>
@@ -17174,32 +17174,32 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>Tìm truyện có bối cảnh dị thế đại lục</t>
+          <t>Tìm truyện có bối cảnh dị thế đại lục, trang thái truyện đã hoàn thành</t>
         </is>
       </c>
       <c r="C365" t="n">
         <v>4</v>
       </c>
       <c r="D365" t="n">
-        <v>12764</v>
+        <v>20772</v>
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>Tông Môn Để Cho Ta Thông Gia, Ta Tu Thành Võ Đạo Tuyệt Đỉnh [Convert]</t>
+          <t>Hệ Thống: Để Ngươi Giúp Đồ Đệ Mạnh Lên, Không Có Để Ngươi Vô Địch [Dịch]</t>
         </is>
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>Huyền Huyễn</t>
+          <t>Tiên Hiệp, Huyền Huyễn, Hệ Thống</t>
         </is>
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>Đang ra</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="H365" t="n">
-        <v>10.1914</v>
+        <v>12.1551</v>
       </c>
       <c r="I365" t="inlineStr">
         <is>
@@ -17208,7 +17208,7 @@
       </c>
       <c r="J365" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/12764-tong-mon-de-cho-ta-thong-gia-ta-tu-thanh-vo-dao-tuyet-dinh-convert</t>
+          <t>https://sitruyencv.com/story/20772-he-thong-de-nguoi-giup-do-de-manh-len-khong-co-de-nguoi-vo-dich-dich</t>
         </is>
       </c>
     </row>
@@ -17220,32 +17220,32 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>Tìm truyện có bối cảnh dị thế đại lục</t>
+          <t>Tìm truyện có bối cảnh dị thế đại lục, trang thái truyện đã hoàn thành</t>
         </is>
       </c>
       <c r="C366" t="n">
         <v>5</v>
       </c>
       <c r="D366" t="n">
-        <v>268</v>
+        <v>17994</v>
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>Tuyệt Thế Đường Môn Chi Long Phá Cửu Thiên [Convert]</t>
+          <t>Tinh Không Hợp Thành Sổ Tay [Convert]</t>
         </is>
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>Khoa Huyễn</t>
+          <t>Huyền Huyễn</t>
         </is>
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>Hoàn thành</t>
+          <t>Đang ra</t>
         </is>
       </c>
       <c r="H366" t="n">
-        <v>9.129899999999999</v>
+        <v>12.0493</v>
       </c>
       <c r="I366" t="inlineStr">
         <is>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="J366" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/268-tuyet-the-duong-mon-chi-long-pha-cuu-thien-convert</t>
+          <t>https://sitruyencv.com/story/17994-tinh-khong-hop-thanh-so-tay-convert</t>
         </is>
       </c>
     </row>
@@ -17266,23 +17266,23 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>Tìm truyện có bối cảnh dị thế đại lục</t>
+          <t>Tìm truyện có bối cảnh dị thế đại lục, trang thái truyện đã hoàn thành</t>
         </is>
       </c>
       <c r="C367" t="n">
         <v>6</v>
       </c>
       <c r="D367" t="n">
-        <v>3074</v>
+        <v>18454</v>
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>Trộm Mộ: Bắt Đầu Triệu Hoán Bất Lương Soái, Nộ Tình Tương Tây [Convert]</t>
+          <t>Vô Tận Hàn Đông: Doanh Địa Của Ta Thăng Cấp Vô Hạn [Dịch]</t>
         </is>
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>Huyền Huyễn</t>
+          <t>Hệ Thống, Tây Phương Kỳ Huyễn, Xuyên Sách, Dị Giới, Dị Năng, Mạt Thế</t>
         </is>
       </c>
       <c r="G367" t="inlineStr">
@@ -17291,7 +17291,7 @@
         </is>
       </c>
       <c r="H367" t="n">
-        <v>9.1084</v>
+        <v>12.0234</v>
       </c>
       <c r="I367" t="inlineStr">
         <is>
@@ -17300,7 +17300,7 @@
       </c>
       <c r="J367" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/3074-trom-mo-bat-dau-trieu-hoan-bat-luong-soai-no-tinh-tuong-tay-convert</t>
+          <t>https://sitruyencv.com/story/18454-vo-tan-han-dong-doanh-dia-cua-ta-thang-cap-vo-han-dich</t>
         </is>
       </c>
     </row>
@@ -17312,32 +17312,32 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Tìm truyện có bối cảnh dị thế đại lục</t>
+          <t>Tìm truyện có bối cảnh dị thế đại lục, trang thái truyện đã hoàn thành</t>
         </is>
       </c>
       <c r="C368" t="n">
         <v>7</v>
       </c>
       <c r="D368" t="n">
-        <v>12428</v>
+        <v>18853</v>
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>Đấu La: Thần Cấp Máy Gian Lận, Rời Núi Tức Vô Địch [Convert]</t>
+          <t>Tây Du: Bắt Đầu Từ Công Chiếu Đại Thoại Tây Du [Dịch]</t>
         </is>
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>Đồng Nhân</t>
+          <t>Tiên Hiệp, Huyền Huyễn, Đồng Nhân, Hệ Thống</t>
         </is>
       </c>
       <c r="G368" t="inlineStr">
         <is>
-          <t>Đang ra</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="H368" t="n">
-        <v>8.968</v>
+        <v>11.8284</v>
       </c>
       <c r="I368" t="inlineStr">
         <is>
@@ -17346,7 +17346,7 @@
       </c>
       <c r="J368" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/12428-dau-la-than-cap-may-gian-lan-roi-nui-tuc-vo-dich-convert</t>
+          <t>https://sitruyencv.com/story/18853-tay-du-bat-dau-tu-cong-chieu-dai-thoai-tay-du-dich</t>
         </is>
       </c>
     </row>
@@ -17358,23 +17358,23 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Tìm truyện có bối cảnh dị thế đại lục</t>
+          <t>Tìm truyện có bối cảnh dị thế đại lục, trang thái truyện đã hoàn thành</t>
         </is>
       </c>
       <c r="C369" t="n">
         <v>8</v>
       </c>
       <c r="D369" t="n">
-        <v>541</v>
+        <v>127</v>
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>Phát Sóng Trực Tiếp Cực Phẩm Âm Dương Sư [Convert]</t>
+          <t>Tối Cường Trang Bức Đả Kiểm Hệ Thống [Convert]</t>
         </is>
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>Đô Thị</t>
+          <t>Tiên Hiệp</t>
         </is>
       </c>
       <c r="G369" t="inlineStr">
@@ -17383,7 +17383,7 @@
         </is>
       </c>
       <c r="H369" t="n">
-        <v>8.9078</v>
+        <v>11.8168</v>
       </c>
       <c r="I369" t="inlineStr">
         <is>
@@ -17392,7 +17392,7 @@
       </c>
       <c r="J369" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/541-phat-song-truc-tiep-cuc-pham-am-duong-su-convert</t>
+          <t>https://sitruyencv.com/story/127-toi-cuong-trang-buc-da-kiem-he-thong-convert</t>
         </is>
       </c>
     </row>
@@ -17404,23 +17404,23 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Tìm truyện có bối cảnh dị thế đại lục</t>
+          <t>Tìm truyện có bối cảnh dị thế đại lục, trang thái truyện đã hoàn thành</t>
         </is>
       </c>
       <c r="C370" t="n">
         <v>9</v>
       </c>
       <c r="D370" t="n">
-        <v>15995</v>
+        <v>15905</v>
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>Tận Thế Cầu Sinh: Ta Có Thể Thăng Hoa Vạn Vật [Convert]</t>
+          <t>Toàn Dân Đầu Tư Thời Đại: Chỉ Có Ta Biết Nhân Vật Chính [Convert]</t>
         </is>
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>Đô Thị</t>
+          <t>Huyền Huyễn</t>
         </is>
       </c>
       <c r="G370" t="inlineStr">
@@ -17429,7 +17429,7 @@
         </is>
       </c>
       <c r="H370" t="n">
-        <v>8.6654</v>
+        <v>11.8081</v>
       </c>
       <c r="I370" t="inlineStr">
         <is>
@@ -17438,7 +17438,7 @@
       </c>
       <c r="J370" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/15995-tan-the-cau-sinh-ta-co-the-thang-hoa-van-vat-convert</t>
+          <t>https://sitruyencv.com/story/15905-toan-dan-dau-tu-thoi-dai-chi-co-ta-biet-nhan-vat-chinh-convert</t>
         </is>
       </c>
     </row>
@@ -17450,23 +17450,23 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Tìm truyện có bối cảnh dị thế đại lục</t>
+          <t>Tìm truyện có bối cảnh dị thế đại lục, trang thái truyện đã hoàn thành</t>
         </is>
       </c>
       <c r="C371" t="n">
         <v>10</v>
       </c>
       <c r="D371" t="n">
-        <v>9820</v>
+        <v>10623</v>
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>Bắt Đầu Mười Liên Rút Sau Đó Vô Địch [Convert]</t>
+          <t>Đấu Phá: Đa Tử Đa Phúc, Ta Chế Tạo Mạnh Nhất Gia Tộc [Convert]</t>
         </is>
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>Huyền Huyễn</t>
+          <t>Đồng Nhân</t>
         </is>
       </c>
       <c r="G371" t="inlineStr">
@@ -17475,7 +17475,7 @@
         </is>
       </c>
       <c r="H371" t="n">
-        <v>8.6128</v>
+        <v>11.0868</v>
       </c>
       <c r="I371" t="inlineStr">
         <is>
@@ -17484,7 +17484,7 @@
       </c>
       <c r="J371" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/9820-bat-dau-muoi-lien-rut-sau-do-vo-dich-convert</t>
+          <t>https://sitruyencv.com/story/10623-dau-pha-da-tu-da-phuc-ta-che-tao-manh-nhat-gia-toc-convert</t>
         </is>
       </c>
     </row>
@@ -17496,7 +17496,7 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Tìm truyện đô thị có yếu tố dị năng</t>
+          <t>Tìm truyện đô thị có yếu tố dị năng có hơn 300 chương</t>
         </is>
       </c>
       <c r="C372" t="n">
@@ -17542,32 +17542,32 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Tìm truyện đô thị có yếu tố dị năng</t>
+          <t>Tìm truyện đô thị có yếu tố dị năng có hơn 300 chương</t>
         </is>
       </c>
       <c r="C373" t="n">
         <v>2</v>
       </c>
       <c r="D373" t="n">
-        <v>19710</v>
+        <v>9529</v>
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>Sau Ly Hôn, Họ Lại Theo Đuổi Tôi [Dịch]</t>
+          <t>Trực Tiếp Thiết Kế Tử Vong [Convert]</t>
         </is>
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>Đô Thị, Sủng</t>
+          <t>Đô Thị</t>
         </is>
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>Đang ra</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="H373" t="n">
-        <v>9.682499999999999</v>
+        <v>10.2817</v>
       </c>
       <c r="I373" t="inlineStr">
         <is>
@@ -17576,7 +17576,7 @@
       </c>
       <c r="J373" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/19710-sau-ly-hon-ho-lai-theo-duoi-toi-dich</t>
+          <t>https://sitruyencv.com/story/9529-truc-tiep-thiet-ke-tu-vong-convert</t>
         </is>
       </c>
     </row>
@@ -17588,32 +17588,32 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>Tìm truyện đô thị có yếu tố dị năng</t>
+          <t>Tìm truyện đô thị có yếu tố dị năng có hơn 300 chương</t>
         </is>
       </c>
       <c r="C374" t="n">
         <v>3</v>
       </c>
       <c r="D374" t="n">
-        <v>17650</v>
+        <v>19710</v>
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>Toàn Dân Hôn Phối: Tốt Nghiệp Phát Lão Bà, Chơi Hỏng Long Nương [Convert]</t>
+          <t>Sau Ly Hôn, Họ Lại Theo Đuổi Tôi [Dịch]</t>
         </is>
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>Đô Thị</t>
+          <t>Đô Thị, Sủng</t>
         </is>
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>Hoàn thành</t>
+          <t>Đang ra</t>
         </is>
       </c>
       <c r="H374" t="n">
-        <v>9.530099999999999</v>
+        <v>9.682499999999999</v>
       </c>
       <c r="I374" t="inlineStr">
         <is>
@@ -17622,7 +17622,7 @@
       </c>
       <c r="J374" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/17650-toan-dan-hon-phoi-tot-nghiep-phat-lao-ba-choi-hong-long-nuong-convert</t>
+          <t>https://sitruyencv.com/story/19710-sau-ly-hon-ho-lai-theo-duoi-toi-dich</t>
         </is>
       </c>
     </row>
@@ -17634,18 +17634,18 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>Tìm truyện đô thị có yếu tố dị năng</t>
+          <t>Tìm truyện đô thị có yếu tố dị năng có hơn 300 chương</t>
         </is>
       </c>
       <c r="C375" t="n">
         <v>4</v>
       </c>
       <c r="D375" t="n">
-        <v>15839</v>
+        <v>17650</v>
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>Mệnh Còn Lại Hai Năm, Bảy Cái Tỷ Tỷ Quỳ Cầu Ta Tha Thứ [Convert]</t>
+          <t>Toàn Dân Hôn Phối: Tốt Nghiệp Phát Lão Bà, Chơi Hỏng Long Nương [Convert]</t>
         </is>
       </c>
       <c r="F375" t="inlineStr">
@@ -17659,7 +17659,7 @@
         </is>
       </c>
       <c r="H375" t="n">
-        <v>8.8811</v>
+        <v>9.530099999999999</v>
       </c>
       <c r="I375" t="inlineStr">
         <is>
@@ -17668,7 +17668,7 @@
       </c>
       <c r="J375" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/15839-menh-con-lai-hai-nam-bay-cai-ty-ty-quy-cau-ta-tha-thu-convert</t>
+          <t>https://sitruyencv.com/story/17650-toan-dan-hon-phoi-tot-nghiep-phat-lao-ba-choi-hong-long-nuong-convert</t>
         </is>
       </c>
     </row>
@@ -17680,23 +17680,23 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>Tìm truyện đô thị có yếu tố dị năng</t>
+          <t>Tìm truyện đô thị có yếu tố dị năng có hơn 300 chương</t>
         </is>
       </c>
       <c r="C376" t="n">
         <v>5</v>
       </c>
       <c r="D376" t="n">
-        <v>19982</v>
+        <v>12225</v>
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>Gia Tộc Tu Tiên: Ta Lấy Luân Hồi Chuyển Thế Tìm Trường Sinh [Convert]</t>
+          <t>Bắt Đầu Bị Quăng, Ta Quay Người Trở Thành Ức Vạn Phú Ông [Convert]</t>
         </is>
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>Tiên Hiệp</t>
+          <t>Đô Thị</t>
         </is>
       </c>
       <c r="G376" t="inlineStr">
@@ -17705,7 +17705,7 @@
         </is>
       </c>
       <c r="H376" t="n">
-        <v>8.0101</v>
+        <v>9.413</v>
       </c>
       <c r="I376" t="inlineStr">
         <is>
@@ -17714,7 +17714,7 @@
       </c>
       <c r="J376" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/19982-gia-toc-tu-tien-ta-lay-luan-hoi-chuyen-the-tim-truong-sinh-convert</t>
+          <t>https://sitruyencv.com/story/12225-bat-dau-bi-quang-ta-quay-nguoi-tro-thanh-uc-van-phu-ong-convert</t>
         </is>
       </c>
     </row>
@@ -17726,18 +17726,18 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>Tìm truyện đô thị có yếu tố dị năng</t>
+          <t>Tìm truyện đô thị có yếu tố dị năng có hơn 300 chương</t>
         </is>
       </c>
       <c r="C377" t="n">
         <v>6</v>
       </c>
       <c r="D377" t="n">
-        <v>13494</v>
+        <v>15839</v>
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>Bức Ta Thoát Khỏi Đội? Mang Bốn Con Chó Một Dạng Đánh! [Convert]</t>
+          <t>Mệnh Còn Lại Hai Năm, Bảy Cái Tỷ Tỷ Quỳ Cầu Ta Tha Thứ [Convert]</t>
         </is>
       </c>
       <c r="F377" t="inlineStr">
@@ -17747,11 +17747,11 @@
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>Đang ra</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="H377" t="n">
-        <v>7.8866</v>
+        <v>8.8811</v>
       </c>
       <c r="I377" t="inlineStr">
         <is>
@@ -17760,7 +17760,7 @@
       </c>
       <c r="J377" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/13494-buc-ta-thoat-khoi-doi-mang-bon-con-cho-mot-dang-danh-convert</t>
+          <t>https://sitruyencv.com/story/15839-menh-con-lai-hai-nam-bay-cai-ty-ty-quy-cau-ta-tha-thu-convert</t>
         </is>
       </c>
     </row>
@@ -17772,23 +17772,23 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>Tìm truyện đô thị có yếu tố dị năng</t>
+          <t>Tìm truyện đô thị có yếu tố dị năng có hơn 300 chương</t>
         </is>
       </c>
       <c r="C378" t="n">
         <v>7</v>
       </c>
       <c r="D378" t="n">
-        <v>18919</v>
+        <v>14073</v>
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>Hoa Ngu: Sự Đản Sinh Của Một Đỉnh Lưu Mị Ma [Convert]</t>
+          <t>One Piece: Ta Đã Nứt Ra, Nhưng Biến Dị Thiên Phú Siêu Cường [Convert]</t>
         </is>
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>Đô Thị</t>
+          <t>Đồng Nhân</t>
         </is>
       </c>
       <c r="G378" t="inlineStr">
@@ -17797,7 +17797,7 @@
         </is>
       </c>
       <c r="H378" t="n">
-        <v>7.8784</v>
+        <v>8.7387</v>
       </c>
       <c r="I378" t="inlineStr">
         <is>
@@ -17806,7 +17806,7 @@
       </c>
       <c r="J378" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/18919-hoa-ngu-su-dan-sinh-cua-mot-dinh-luu-mi-ma-convert</t>
+          <t>https://sitruyencv.com/story/14073-one-piece-ta-da-nut-ra-nhung-bien-di-thien-phu-sieu-cuong-convert</t>
         </is>
       </c>
     </row>
@@ -17818,18 +17818,18 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>Tìm truyện đô thị có yếu tố dị năng</t>
+          <t>Tìm truyện đô thị có yếu tố dị năng có hơn 300 chương</t>
         </is>
       </c>
       <c r="C379" t="n">
         <v>8</v>
       </c>
       <c r="D379" t="n">
-        <v>14998</v>
+        <v>17739</v>
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>Cao Khảo Sau Đó, Ta Lại Bị Quốc Gia Sss Cấp Mã Hóa [Convert]</t>
+          <t>Tận Thế: Xuyên Qua Gấu Bắc Cực, Nuốt Vào Trái Nikyu Nikyu No Mi [Convert]</t>
         </is>
       </c>
       <c r="F379" t="inlineStr">
@@ -17843,7 +17843,7 @@
         </is>
       </c>
       <c r="H379" t="n">
-        <v>7.6801</v>
+        <v>8.6861</v>
       </c>
       <c r="I379" t="inlineStr">
         <is>
@@ -17852,7 +17852,7 @@
       </c>
       <c r="J379" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/14998-cao-khao-sau-do-ta-lai-bi-quoc-gia-sss-cap-ma-hoa-convert</t>
+          <t>https://sitruyencv.com/story/17739-tan-the-xuyen-qua-gau-bac-cuc-nuot-vao-trai-nikyu-nikyu-no-mi-convert</t>
         </is>
       </c>
     </row>
@@ -17864,32 +17864,32 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>Tìm truyện đô thị có yếu tố dị năng</t>
+          <t>Tìm truyện đô thị có yếu tố dị năng có hơn 300 chương</t>
         </is>
       </c>
       <c r="C380" t="n">
         <v>9</v>
       </c>
       <c r="D380" t="n">
-        <v>20799</v>
+        <v>19897</v>
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>Ta Là Đạo Sĩ Mao Sơn, Sao Toàn Là Tà Thuật [Dịch]</t>
+          <t>Quốc Vận Cầu Sinh: Vận Khí Của Ta Xui Hơn Ức Điểm Điểm [Convert]</t>
         </is>
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>Đô Thị, Huyền Huyễn, Kỳ Ảo, Tây Phương Kỳ Huyễn, Linh Dị, Huyền Nghi Thần Quái, Lãng Mạn Thanh Xuân</t>
+          <t>Đô Thị</t>
         </is>
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>Hoàn thành</t>
+          <t>Đang ra</t>
         </is>
       </c>
       <c r="H380" t="n">
-        <v>7.5767</v>
+        <v>8.468999999999999</v>
       </c>
       <c r="I380" t="inlineStr">
         <is>
@@ -17898,7 +17898,7 @@
       </c>
       <c r="J380" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/20799-ta-la-dao-si-mao-son-sao-toan-la-ta-thuat-dich</t>
+          <t>https://sitruyencv.com/story/19897-quoc-van-cau-sinh-van-khi-cua-ta-xui-hon-uc-diem-diem-convert</t>
         </is>
       </c>
     </row>
@@ -17910,18 +17910,18 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>Tìm truyện đô thị có yếu tố dị năng</t>
+          <t>Tìm truyện đô thị có yếu tố dị năng có hơn 300 chương</t>
         </is>
       </c>
       <c r="C381" t="n">
         <v>10</v>
       </c>
       <c r="D381" t="n">
-        <v>15995</v>
+        <v>13084</v>
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>Tận Thế Cầu Sinh: Ta Có Thể Thăng Hoa Vạn Vật [Convert]</t>
+          <t>Bình Nguyên Cầu Sinh: Ta Mỗi Ngày Đổi Mới Một Cái Tình Báo Nhỏ [Convert]</t>
         </is>
       </c>
       <c r="F381" t="inlineStr">
@@ -17935,7 +17935,7 @@
         </is>
       </c>
       <c r="H381" t="n">
-        <v>7.5617</v>
+        <v>8.2354</v>
       </c>
       <c r="I381" t="inlineStr">
         <is>
@@ -17944,7 +17944,7 @@
       </c>
       <c r="J381" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/15995-tan-the-cau-sinh-ta-co-the-thang-hoa-van-vat-convert</t>
+          <t>https://sitruyencv.com/story/13084-binh-nguyen-cau-sinh-ta-moi-ngay-doi-moi-mot-cai-tinh-bao-nho-convert</t>
         </is>
       </c>
     </row>
@@ -17956,32 +17956,32 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>Tìm truyện có phong cách thiết huyết</t>
+          <t>Tìm truyện có phong cách thiết huyết có ít hơn 1500 chương</t>
         </is>
       </c>
       <c r="C382" t="n">
         <v>1</v>
       </c>
       <c r="D382" t="n">
-        <v>14198</v>
+        <v>9529</v>
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>Vừa Thành Phong Hào Đấu La, Đạo Lữ Hệ Thống Tìm Tới Cửa! [Convert]</t>
+          <t>Trực Tiếp Thiết Kế Tử Vong [Convert]</t>
         </is>
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>Đồng Nhân</t>
+          <t>Đô Thị</t>
         </is>
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>Đang ra</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="H382" t="n">
-        <v>8.6934</v>
+        <v>13.4027</v>
       </c>
       <c r="I382" t="inlineStr">
         <is>
@@ -17990,7 +17990,7 @@
       </c>
       <c r="J382" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/14198-vua-thanh-phong-hao-dau-la-dao-lu-he-thong-tim-toi-cua-convert</t>
+          <t>https://sitruyencv.com/story/9529-truc-tiep-thiet-ke-tu-vong-convert</t>
         </is>
       </c>
     </row>
@@ -18002,23 +18002,23 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>Tìm truyện có phong cách thiết huyết</t>
+          <t>Tìm truyện có phong cách thiết huyết có ít hơn 1500 chương</t>
         </is>
       </c>
       <c r="C383" t="n">
         <v>2</v>
       </c>
       <c r="D383" t="n">
-        <v>14007</v>
+        <v>17762</v>
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>Cửu Giai phù Lục sư [Convert]</t>
+          <t>Ta Sáng Lập Siêu Phàm Thời Đại [Convert]</t>
         </is>
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>Tiên Hiệp</t>
+          <t>Khoa Huyễn</t>
         </is>
       </c>
       <c r="G383" t="inlineStr">
@@ -18027,7 +18027,7 @@
         </is>
       </c>
       <c r="H383" t="n">
-        <v>6.9626</v>
+        <v>9.179500000000001</v>
       </c>
       <c r="I383" t="inlineStr">
         <is>
@@ -18036,7 +18036,7 @@
       </c>
       <c r="J383" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/14007-cuu-giai-phu-luc-su-convert</t>
+          <t>https://sitruyencv.com/story/17762-ta-sang-lap-sieu-pham-thoi-dai-convert</t>
         </is>
       </c>
     </row>
@@ -18048,23 +18048,23 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>Tìm truyện có phong cách thiết huyết</t>
+          <t>Tìm truyện có phong cách thiết huyết có ít hơn 1500 chương</t>
         </is>
       </c>
       <c r="C384" t="n">
         <v>3</v>
       </c>
       <c r="D384" t="n">
-        <v>13886</v>
+        <v>14198</v>
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>Độc Thủ Cứ Điểm Ba Năm, Ta Thành Đêm Dài Lãnh Chúa [Convert]</t>
+          <t>Vừa Thành Phong Hào Đấu La, Đạo Lữ Hệ Thống Tìm Tới Cửa! [Convert]</t>
         </is>
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>Khoa Huyễn</t>
+          <t>Đồng Nhân</t>
         </is>
       </c>
       <c r="G384" t="inlineStr">
@@ -18073,7 +18073,7 @@
         </is>
       </c>
       <c r="H384" t="n">
-        <v>6.3458</v>
+        <v>8.6934</v>
       </c>
       <c r="I384" t="inlineStr">
         <is>
@@ -18082,7 +18082,7 @@
       </c>
       <c r="J384" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/13886-doc-thu-cu-diem-ba-nam-ta-thanh-dem-dai-lanh-chua-convert</t>
+          <t>https://sitruyencv.com/story/14198-vua-thanh-phong-hao-dau-la-dao-lu-he-thong-tim-toi-cua-convert</t>
         </is>
       </c>
     </row>
@@ -18094,32 +18094,32 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Tìm truyện có phong cách thiết huyết</t>
+          <t>Tìm truyện có phong cách thiết huyết có ít hơn 1500 chương</t>
         </is>
       </c>
       <c r="C385" t="n">
         <v>4</v>
       </c>
       <c r="D385" t="n">
-        <v>17792</v>
+        <v>11918</v>
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>Ta Câu Thông Tương Lai, Giết Xuyên Tận Thế Này! [Convert]</t>
+          <t>Ngự Thú Tiến Hóa Thương [Convert]</t>
         </is>
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>Huyền Nghi</t>
+          <t>Huyền Huyễn</t>
         </is>
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>Đang ra</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="H385" t="n">
-        <v>6.225</v>
+        <v>8.0321</v>
       </c>
       <c r="I385" t="inlineStr">
         <is>
@@ -18128,7 +18128,7 @@
       </c>
       <c r="J385" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/17792-ta-cau-thong-tuong-lai-giet-xuyen-tan-the-nay-convert</t>
+          <t>https://sitruyencv.com/story/11918-ngu-thu-tien-hoa-thuong-convert</t>
         </is>
       </c>
     </row>
@@ -18140,7 +18140,7 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>Tìm truyện có phong cách thiết huyết</t>
+          <t>Tìm truyện có phong cách thiết huyết có ít hơn 1500 chương</t>
         </is>
       </c>
       <c r="C386" t="n">
@@ -18165,7 +18165,7 @@
         </is>
       </c>
       <c r="H386" t="n">
-        <v>6.1474</v>
+        <v>7.9269</v>
       </c>
       <c r="I386" t="inlineStr">
         <is>
@@ -18186,18 +18186,18 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Tìm truyện có phong cách thiết huyết</t>
+          <t>Tìm truyện có phong cách thiết huyết có ít hơn 1500 chương</t>
         </is>
       </c>
       <c r="C387" t="n">
         <v>6</v>
       </c>
       <c r="D387" t="n">
-        <v>19397</v>
+        <v>20650</v>
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>Đa Tử Đa Phúc, Thập Nhị Tổ Vu Bức Hôn Toàn Hồng Hoang [Convert]</t>
+          <t>Vạn Lần Hoàn Trả, Lão Phu Tuổi Già Đi Làm Liếm Cẩu [Dịch]</t>
         </is>
       </c>
       <c r="F387" t="inlineStr">
@@ -18207,11 +18207,11 @@
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>Đang ra</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="H387" t="n">
-        <v>6.0968</v>
+        <v>7.5294</v>
       </c>
       <c r="I387" t="inlineStr">
         <is>
@@ -18220,7 +18220,7 @@
       </c>
       <c r="J387" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/19397-da-tu-da-phuc-thap-nhi-to-vu-buc-hon-toan-hong-hoang-convert</t>
+          <t>https://sitruyencv.com/story/20650-van-lan-hoan-tra-lao-phu-tuoi-gia-di-lam-liem-cau-dich</t>
         </is>
       </c>
     </row>
@@ -18232,18 +18232,18 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Tìm truyện có phong cách thiết huyết</t>
+          <t>Tìm truyện có phong cách thiết huyết có ít hơn 1500 chương</t>
         </is>
       </c>
       <c r="C388" t="n">
         <v>7</v>
       </c>
       <c r="D388" t="n">
-        <v>9529</v>
+        <v>13084</v>
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>Trực Tiếp Thiết Kế Tử Vong [Convert]</t>
+          <t>Bình Nguyên Cầu Sinh: Ta Mỗi Ngày Đổi Mới Một Cái Tình Báo Nhỏ [Convert]</t>
         </is>
       </c>
       <c r="F388" t="inlineStr">
@@ -18253,11 +18253,11 @@
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>Hoàn thành</t>
+          <t>Đang ra</t>
         </is>
       </c>
       <c r="H388" t="n">
-        <v>6.0328</v>
+        <v>7.4317</v>
       </c>
       <c r="I388" t="inlineStr">
         <is>
@@ -18266,7 +18266,7 @@
       </c>
       <c r="J388" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/9529-truc-tiep-thiet-ke-tu-vong-convert</t>
+          <t>https://sitruyencv.com/story/13084-binh-nguyen-cau-sinh-ta-moi-ngay-doi-moi-mot-cai-tinh-bao-nho-convert</t>
         </is>
       </c>
     </row>
@@ -18278,32 +18278,32 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>Tìm truyện có phong cách thiết huyết</t>
+          <t>Tìm truyện có phong cách thiết huyết có ít hơn 1500 chương</t>
         </is>
       </c>
       <c r="C389" t="n">
         <v>8</v>
       </c>
       <c r="D389" t="n">
-        <v>17916</v>
+        <v>16201</v>
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>Từ Thiết Y Công Bắt Đầu Nhục Thân Thành Thánh [Convert]</t>
+          <t>Nữ Hiệp Xin Dừng Tay [Convert]</t>
         </is>
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>Huyền Huyễn</t>
+          <t>Dã Sử</t>
         </is>
       </c>
       <c r="G389" t="inlineStr">
         <is>
-          <t>Đang ra</t>
+          <t>Tạm dừng</t>
         </is>
       </c>
       <c r="H389" t="n">
-        <v>5.9439</v>
+        <v>7.2004</v>
       </c>
       <c r="I389" t="inlineStr">
         <is>
@@ -18312,7 +18312,7 @@
       </c>
       <c r="J389" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/17916-tu-thiet-y-cong-bat-dau-nhuc-than-thanh-thanh-convert</t>
+          <t>https://sitruyencv.com/story/16201-nu-hiep-xin-dung-tay-convert</t>
         </is>
       </c>
     </row>
@@ -18324,32 +18324,32 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>Tìm truyện có phong cách thiết huyết</t>
+          <t>Tìm truyện có phong cách thiết huyết có ít hơn 1500 chương</t>
         </is>
       </c>
       <c r="C390" t="n">
         <v>9</v>
       </c>
       <c r="D390" t="n">
-        <v>17785</v>
+        <v>171</v>
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>Võng Du: Ta Ở Trong Game Làm Quan Sai [Convert]</t>
+          <t>Thời Trung Cổ Truyền Kỳ Thợ Săn Quỷ [Convert]</t>
         </is>
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>Võng Du</t>
+          <t>Tây Phương Kỳ Huyễn</t>
         </is>
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>Hoàn thành</t>
+          <t>Đang ra</t>
         </is>
       </c>
       <c r="H390" t="n">
-        <v>5.5822</v>
+        <v>7.0716</v>
       </c>
       <c r="I390" t="inlineStr">
         <is>
@@ -18358,7 +18358,7 @@
       </c>
       <c r="J390" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/17785-vong-du-ta-o-trong-game-lam-quan-sai-convert</t>
+          <t>https://sitruyencv.com/story/171-thoi-trung-co-truyen-ky-tho-san-quy-convert</t>
         </is>
       </c>
     </row>
@@ -18370,23 +18370,23 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>Tìm truyện có phong cách thiết huyết</t>
+          <t>Tìm truyện có phong cách thiết huyết có ít hơn 1500 chương</t>
         </is>
       </c>
       <c r="C391" t="n">
         <v>10</v>
       </c>
       <c r="D391" t="n">
-        <v>13084</v>
+        <v>14007</v>
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>Bình Nguyên Cầu Sinh: Ta Mỗi Ngày Đổi Mới Một Cái Tình Báo Nhỏ [Convert]</t>
+          <t>Cửu Giai phù Lục sư [Convert]</t>
         </is>
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>Đô Thị</t>
+          <t>Tiên Hiệp</t>
         </is>
       </c>
       <c r="G391" t="inlineStr">
@@ -18395,7 +18395,7 @@
         </is>
       </c>
       <c r="H391" t="n">
-        <v>5.5137</v>
+        <v>6.9626</v>
       </c>
       <c r="I391" t="inlineStr">
         <is>
@@ -18404,7 +18404,7 @@
       </c>
       <c r="J391" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/13084-binh-nguyen-cau-sinh-ta-moi-ngay-doi-moi-mot-cai-tinh-bao-nho-convert</t>
+          <t>https://sitruyencv.com/story/14007-cuu-giai-phu-luc-su-convert</t>
         </is>
       </c>
     </row>
@@ -18416,18 +18416,18 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>Tìm truyện có nhân vật chính là thiên tài</t>
+          <t>Tìm truyện có nhân vật chính là thiên tài có trạng thái đang ra và hơn 500 chương</t>
         </is>
       </c>
       <c r="C392" t="n">
         <v>1</v>
       </c>
       <c r="D392" t="n">
-        <v>15905</v>
+        <v>11553</v>
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>Toàn Dân Đầu Tư Thời Đại: Chỉ Có Ta Biết Nhân Vật Chính [Convert]</t>
+          <t>Bắt Đầu Kém Chút Bị Ăn, May Mắn Ta Có Thể Dời Đi Mặt Trái Trạng Thái [Convert]</t>
         </is>
       </c>
       <c r="F392" t="inlineStr">
@@ -18441,7 +18441,7 @@
         </is>
       </c>
       <c r="H392" t="n">
-        <v>11.2248</v>
+        <v>14.6807</v>
       </c>
       <c r="I392" t="inlineStr">
         <is>
@@ -18450,7 +18450,7 @@
       </c>
       <c r="J392" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/15905-toan-dan-dau-tu-thoi-dai-chi-co-ta-biet-nhan-vat-chinh-convert</t>
+          <t>https://sitruyencv.com/story/11553-bat-dau-kem-chut-bi-an-may-man-ta-co-the-doi-di-mat-trai-trang-thai-convert</t>
         </is>
       </c>
     </row>
@@ -18462,23 +18462,23 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>Tìm truyện có nhân vật chính là thiên tài</t>
+          <t>Tìm truyện có nhân vật chính là thiên tài có trạng thái đang ra và hơn 500 chương</t>
         </is>
       </c>
       <c r="C393" t="n">
         <v>2</v>
       </c>
       <c r="D393" t="n">
-        <v>16145</v>
+        <v>15905</v>
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>Liếm Cẩu Phản Diện Chỉ Nghĩ Cẩu , Nữ Chính Không Theo Sáo Lộ Đi [Convert]</t>
+          <t>Toàn Dân Đầu Tư Thời Đại: Chỉ Có Ta Biết Nhân Vật Chính [Convert]</t>
         </is>
       </c>
       <c r="F393" t="inlineStr">
         <is>
-          <t>Đô Thị</t>
+          <t>Huyền Huyễn</t>
         </is>
       </c>
       <c r="G393" t="inlineStr">
@@ -18487,7 +18487,7 @@
         </is>
       </c>
       <c r="H393" t="n">
-        <v>8.9841</v>
+        <v>13.6047</v>
       </c>
       <c r="I393" t="inlineStr">
         <is>
@@ -18496,7 +18496,7 @@
       </c>
       <c r="J393" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/16145-liem-cau-phan-dien-chi-nghi-cau-nu-chinh-khong-theo-sao-lo-di-convert</t>
+          <t>https://sitruyencv.com/story/15905-toan-dan-dau-tu-thoi-dai-chi-co-ta-biet-nhan-vat-chinh-convert</t>
         </is>
       </c>
     </row>
@@ -18508,18 +18508,18 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Tìm truyện có nhân vật chính là thiên tài</t>
+          <t>Tìm truyện có nhân vật chính là thiên tài có trạng thái đang ra và hơn 500 chương</t>
         </is>
       </c>
       <c r="C394" t="n">
         <v>3</v>
       </c>
       <c r="D394" t="n">
-        <v>19982</v>
+        <v>13674</v>
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>Gia Tộc Tu Tiên: Ta Lấy Luân Hồi Chuyển Thế Tìm Trường Sinh [Convert]</t>
+          <t>Vạn Thú Thế Gia Quật Khởi [Convert]</t>
         </is>
       </c>
       <c r="F394" t="inlineStr">
@@ -18533,7 +18533,7 @@
         </is>
       </c>
       <c r="H394" t="n">
-        <v>8.3086</v>
+        <v>12.4727</v>
       </c>
       <c r="I394" t="inlineStr">
         <is>
@@ -18542,7 +18542,7 @@
       </c>
       <c r="J394" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/19982-gia-toc-tu-tien-ta-lay-luan-hoi-chuyen-the-tim-truong-sinh-convert</t>
+          <t>https://sitruyencv.com/story/13674-van-thu-the-gia-quat-khoi-convert</t>
         </is>
       </c>
     </row>
@@ -18554,18 +18554,18 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Tìm truyện có nhân vật chính là thiên tài</t>
+          <t>Tìm truyện có nhân vật chính là thiên tài có trạng thái đang ra và hơn 500 chương</t>
         </is>
       </c>
       <c r="C395" t="n">
         <v>4</v>
       </c>
       <c r="D395" t="n">
-        <v>16838</v>
+        <v>17365</v>
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>Tu Tiên: Trùng Sinh Dị Giới Chế Tạo Tối Cường Tông Môn [Convert]</t>
+          <t>Ta Có Một Gốc Thần Thoại Thụ [Convert]</t>
         </is>
       </c>
       <c r="F395" t="inlineStr">
@@ -18579,7 +18579,7 @@
         </is>
       </c>
       <c r="H395" t="n">
-        <v>7.9886</v>
+        <v>12.3184</v>
       </c>
       <c r="I395" t="inlineStr">
         <is>
@@ -18588,7 +18588,7 @@
       </c>
       <c r="J395" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/16838-tu-tien-trung-sinh-di-gioi-che-tao-toi-cuong-tong-mon-convert</t>
+          <t>https://sitruyencv.com/story/17365-ta-co-mot-goc-than-thoai-thu-convert</t>
         </is>
       </c>
     </row>
@@ -18600,23 +18600,23 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Tìm truyện có nhân vật chính là thiên tài</t>
+          <t>Tìm truyện có nhân vật chính là thiên tài có trạng thái đang ra và hơn 500 chương</t>
         </is>
       </c>
       <c r="C396" t="n">
         <v>5</v>
       </c>
       <c r="D396" t="n">
-        <v>18937</v>
+        <v>13905</v>
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>Hồng Mông Bá Thể Quyết [Dịch]</t>
+          <t>Mệnh Cách Thiên Đạo Thù Cần, Cũng May Ta Là Thiên Tài [Convert]</t>
         </is>
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>Tiên Hiệp, Huyền Huyễn</t>
+          <t>Huyền Huyễn</t>
         </is>
       </c>
       <c r="G396" t="inlineStr">
@@ -18625,7 +18625,7 @@
         </is>
       </c>
       <c r="H396" t="n">
-        <v>7.7241</v>
+        <v>11.8427</v>
       </c>
       <c r="I396" t="inlineStr">
         <is>
@@ -18634,7 +18634,7 @@
       </c>
       <c r="J396" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/18937-hong-mong-ba-the-quyet-dich</t>
+          <t>https://sitruyencv.com/story/13905-menh-cach-thien-dao-thu-can-cung-may-ta-la-thien-tai-convert</t>
         </is>
       </c>
     </row>
@@ -18646,32 +18646,32 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Tìm truyện có nhân vật chính là thiên tài</t>
+          <t>Tìm truyện có nhân vật chính là thiên tài có trạng thái đang ra và hơn 500 chương</t>
         </is>
       </c>
       <c r="C397" t="n">
         <v>6</v>
       </c>
       <c r="D397" t="n">
-        <v>14198</v>
+        <v>11918</v>
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>Vừa Thành Phong Hào Đấu La, Đạo Lữ Hệ Thống Tìm Tới Cửa! [Convert]</t>
+          <t>Ngự Thú Tiến Hóa Thương [Convert]</t>
         </is>
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>Đồng Nhân</t>
+          <t>Huyền Huyễn</t>
         </is>
       </c>
       <c r="G397" t="inlineStr">
         <is>
-          <t>Đang ra</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="H397" t="n">
-        <v>7.4202</v>
+        <v>11.3963</v>
       </c>
       <c r="I397" t="inlineStr">
         <is>
@@ -18680,7 +18680,7 @@
       </c>
       <c r="J397" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/14198-vua-thanh-phong-hao-dau-la-dao-lu-he-thong-tim-toi-cua-convert</t>
+          <t>https://sitruyencv.com/story/11918-ngu-thu-tien-hoa-thuong-convert</t>
         </is>
       </c>
     </row>
@@ -18692,23 +18692,23 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Tìm truyện có nhân vật chính là thiên tài</t>
+          <t>Tìm truyện có nhân vật chính là thiên tài có trạng thái đang ra và hơn 500 chương</t>
         </is>
       </c>
       <c r="C398" t="n">
         <v>7</v>
       </c>
       <c r="D398" t="n">
-        <v>20777</v>
+        <v>13561</v>
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>Bậc Thầy Đóng Vai: Bắt Đầu Từ Chuyên Gia Chia Tay [Dịch]</t>
+          <t>Sau Khi Sống Lại Mới Phát Hiện, Ta Đúng Là Thiên Mệnh Nhân Vật Chính! [Convert]</t>
         </is>
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>Đô Thị</t>
+          <t>Huyền Huyễn</t>
         </is>
       </c>
       <c r="G398" t="inlineStr">
@@ -18717,7 +18717,7 @@
         </is>
       </c>
       <c r="H398" t="n">
-        <v>7.1989</v>
+        <v>11.1715</v>
       </c>
       <c r="I398" t="inlineStr">
         <is>
@@ -18726,7 +18726,7 @@
       </c>
       <c r="J398" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/20777-bac-thay-dong-vai-bat-dau-tu-chuyen-gia-chia-tay-dich</t>
+          <t>https://sitruyencv.com/story/13561-sau-khi-song-lai-moi-phat-hien-ta-dung-la-thien-menh-nhan-vat-chinh-convert</t>
         </is>
       </c>
     </row>
@@ -18738,18 +18738,18 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>Tìm truyện có nhân vật chính là thiên tài</t>
+          <t>Tìm truyện có nhân vật chính là thiên tài có trạng thái đang ra và hơn 500 chương</t>
         </is>
       </c>
       <c r="C399" t="n">
         <v>8</v>
       </c>
       <c r="D399" t="n">
-        <v>15045</v>
+        <v>16838</v>
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>Huyền Huyễn: Ta! Thiên Mệnh Đại Nhân Vật Phản Phái [Convert]</t>
+          <t>Tu Tiên: Trùng Sinh Dị Giới Chế Tạo Tối Cường Tông Môn [Convert]</t>
         </is>
       </c>
       <c r="F399" t="inlineStr">
@@ -18759,11 +18759,11 @@
       </c>
       <c r="G399" t="inlineStr">
         <is>
-          <t>Tạm dừng</t>
+          <t>Đang ra</t>
         </is>
       </c>
       <c r="H399" t="n">
-        <v>7.178</v>
+        <v>10.6992</v>
       </c>
       <c r="I399" t="inlineStr">
         <is>
@@ -18772,7 +18772,7 @@
       </c>
       <c r="J399" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/15045-huyen-huyen-ta-thien-menh-dai-nhan-vat-phan-phai-convert</t>
+          <t>https://sitruyencv.com/story/16838-tu-tien-trung-sinh-di-gioi-che-tao-toi-cuong-tong-mon-convert</t>
         </is>
       </c>
     </row>
@@ -18784,23 +18784,23 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>Tìm truyện có nhân vật chính là thiên tài</t>
+          <t>Tìm truyện có nhân vật chính là thiên tài có trạng thái đang ra và hơn 500 chương</t>
         </is>
       </c>
       <c r="C400" t="n">
         <v>9</v>
       </c>
       <c r="D400" t="n">
-        <v>13905</v>
+        <v>16928</v>
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>Mệnh Cách Thiên Đạo Thù Cần, Cũng May Ta Là Thiên Tài [Convert]</t>
+          <t>Nơi Ẩn Núp Thuyết Tiến Hoá [Convert]</t>
         </is>
       </c>
       <c r="F400" t="inlineStr">
         <is>
-          <t>Huyền Huyễn</t>
+          <t>Đô Thị</t>
         </is>
       </c>
       <c r="G400" t="inlineStr">
@@ -18809,7 +18809,7 @@
         </is>
       </c>
       <c r="H400" t="n">
-        <v>6.9232</v>
+        <v>10.6675</v>
       </c>
       <c r="I400" t="inlineStr">
         <is>
@@ -18818,7 +18818,7 @@
       </c>
       <c r="J400" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/13905-menh-cach-thien-dao-thu-can-cung-may-ta-la-thien-tai-convert</t>
+          <t>https://sitruyencv.com/story/16928-noi-an-nup-thuyet-tien-hoa-convert</t>
         </is>
       </c>
     </row>
@@ -18830,18 +18830,18 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>Tìm truyện có nhân vật chính là thiên tài</t>
+          <t>Tìm truyện có nhân vật chính là thiên tài có trạng thái đang ra và hơn 500 chương</t>
         </is>
       </c>
       <c r="C401" t="n">
         <v>10</v>
       </c>
       <c r="D401" t="n">
-        <v>5138</v>
+        <v>18613</v>
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>Đánh Dấu Già Thiên Trăm Năm Thành Thánh [Convert]</t>
+          <t>Đỉnh Cấp Ngộ Tính: Từ Cơ Sở Quyền Pháp Bắt Đầu [Dịch]</t>
         </is>
       </c>
       <c r="F401" t="inlineStr">
@@ -18855,7 +18855,7 @@
         </is>
       </c>
       <c r="H401" t="n">
-        <v>6.8893</v>
+        <v>10.5747</v>
       </c>
       <c r="I401" t="inlineStr">
         <is>
@@ -18864,7 +18864,7 @@
       </c>
       <c r="J401" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/5138-danh-dau-gia-thien-tram-nam-thanh-thanh-convert</t>
+          <t>https://sitruyencv.com/story/18613-dinh-cap-ngo-tinh-tu-co-so-quyen-phap-bat-dau-dich</t>
         </is>
       </c>
     </row>
@@ -28996,23 +28996,23 @@
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>Tìm truyện có yếu tố đông phương huyền huyễn và hệ thống</t>
+          <t>Tìm truyện có yếu tố đông phương huyền huyễn và hệ thống có trạng thái hoàn thành</t>
         </is>
       </c>
       <c r="C622" t="n">
         <v>1</v>
       </c>
       <c r="D622" t="n">
-        <v>19710</v>
+        <v>11553</v>
       </c>
       <c r="E622" t="inlineStr">
         <is>
-          <t>Sau Ly Hôn, Họ Lại Theo Đuổi Tôi [Dịch]</t>
+          <t>Bắt Đầu Kém Chút Bị Ăn, May Mắn Ta Có Thể Dời Đi Mặt Trái Trạng Thái [Convert]</t>
         </is>
       </c>
       <c r="F622" t="inlineStr">
         <is>
-          <t>Đô Thị, Sủng</t>
+          <t>Huyền Huyễn</t>
         </is>
       </c>
       <c r="G622" t="inlineStr">
@@ -29021,7 +29021,7 @@
         </is>
       </c>
       <c r="H622" t="n">
-        <v>9.271599999999999</v>
+        <v>15.9382</v>
       </c>
       <c r="I622" t="inlineStr">
         <is>
@@ -29030,7 +29030,7 @@
       </c>
       <c r="J622" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/19710-sau-ly-hon-ho-lai-theo-duoi-toi-dich</t>
+          <t>https://sitruyencv.com/story/11553-bat-dau-kem-chut-bi-an-may-man-ta-co-the-doi-di-mat-trai-trang-thai-convert</t>
         </is>
       </c>
     </row>
@@ -29042,7 +29042,7 @@
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>Tìm truyện có yếu tố đông phương huyền huyễn và hệ thống</t>
+          <t>Tìm truyện có yếu tố đông phương huyền huyễn và hệ thống có trạng thái hoàn thành</t>
         </is>
       </c>
       <c r="C623" t="n">
@@ -29067,7 +29067,7 @@
         </is>
       </c>
       <c r="H623" t="n">
-        <v>8.717599999999999</v>
+        <v>11.8712</v>
       </c>
       <c r="I623" t="inlineStr">
         <is>
@@ -29088,23 +29088,23 @@
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>Tìm truyện có yếu tố đông phương huyền huyễn và hệ thống</t>
+          <t>Tìm truyện có yếu tố đông phương huyền huyễn và hệ thống có trạng thái hoàn thành</t>
         </is>
       </c>
       <c r="C624" t="n">
         <v>3</v>
       </c>
       <c r="D624" t="n">
-        <v>19982</v>
+        <v>13237</v>
       </c>
       <c r="E624" t="inlineStr">
         <is>
-          <t>Gia Tộc Tu Tiên: Ta Lấy Luân Hồi Chuyển Thế Tìm Trường Sinh [Convert]</t>
+          <t>Kinh Tiêu [Convert]</t>
         </is>
       </c>
       <c r="F624" t="inlineStr">
         <is>
-          <t>Tiên Hiệp</t>
+          <t>Huyền Huyễn</t>
         </is>
       </c>
       <c r="G624" t="inlineStr">
@@ -29113,7 +29113,7 @@
         </is>
       </c>
       <c r="H624" t="n">
-        <v>8.243600000000001</v>
+        <v>10.657</v>
       </c>
       <c r="I624" t="inlineStr">
         <is>
@@ -29122,7 +29122,7 @@
       </c>
       <c r="J624" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/19982-gia-toc-tu-tien-ta-lay-luan-hoi-chuyen-the-tim-truong-sinh-convert</t>
+          <t>https://sitruyencv.com/story/13237-kinh-tieu-convert</t>
         </is>
       </c>
     </row>
@@ -29134,23 +29134,23 @@
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>Tìm truyện có yếu tố đông phương huyền huyễn và hệ thống</t>
+          <t>Tìm truyện có yếu tố đông phương huyền huyễn và hệ thống có trạng thái hoàn thành</t>
         </is>
       </c>
       <c r="C625" t="n">
         <v>4</v>
       </c>
       <c r="D625" t="n">
-        <v>17533</v>
+        <v>20392</v>
       </c>
       <c r="E625" t="inlineStr">
         <is>
-          <t>Vô Địch Theo Cướp Đoạt Khí Huyết Bắt Đầu [Convert]</t>
+          <t>Nhà Ta Thế Hệ Cường Đạo, Tiểu Tử Ngươi Thi Đậu Trạng Nguyên [Dịch]</t>
         </is>
       </c>
       <c r="F625" t="inlineStr">
         <is>
-          <t>Huyền Huyễn</t>
+          <t>Huyền Huyễn, Cổ Đại</t>
         </is>
       </c>
       <c r="G625" t="inlineStr">
@@ -29159,7 +29159,7 @@
         </is>
       </c>
       <c r="H625" t="n">
-        <v>7.1923</v>
+        <v>10.1689</v>
       </c>
       <c r="I625" t="inlineStr">
         <is>
@@ -29168,7 +29168,7 @@
       </c>
       <c r="J625" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/17533-vo-dich-theo-cuop-doat-khi-huyet-bat-dau-convert</t>
+          <t>https://sitruyencv.com/story/20392-nha-ta-the-he-cuong-dao-tieu-tu-nguoi-thi-dau-trang-nguyen-dich</t>
         </is>
       </c>
     </row>
@@ -29180,18 +29180,18 @@
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>Tìm truyện có yếu tố đông phương huyền huyễn và hệ thống</t>
+          <t>Tìm truyện có yếu tố đông phương huyền huyễn và hệ thống có trạng thái hoàn thành</t>
         </is>
       </c>
       <c r="C626" t="n">
         <v>5</v>
       </c>
       <c r="D626" t="n">
-        <v>13237</v>
+        <v>11481</v>
       </c>
       <c r="E626" t="inlineStr">
         <is>
-          <t>Kinh Tiêu [Convert]</t>
+          <t>Đầu Tư Trọng Sinh Nữ Đế, Nàng Lại Gọi Ta Tướng Công [Convert]</t>
         </is>
       </c>
       <c r="F626" t="inlineStr">
@@ -29201,11 +29201,11 @@
       </c>
       <c r="G626" t="inlineStr">
         <is>
-          <t>Đang ra</t>
+          <t>Tạm dừng</t>
         </is>
       </c>
       <c r="H626" t="n">
-        <v>6.7929</v>
+        <v>10.0815</v>
       </c>
       <c r="I626" t="inlineStr">
         <is>
@@ -29214,7 +29214,7 @@
       </c>
       <c r="J626" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/13237-kinh-tieu-convert</t>
+          <t>https://sitruyencv.com/story/11481-dau-tu-trong-sinh-nu-de-nang-lai-goi-ta-tuong-cong-convert</t>
         </is>
       </c>
     </row>
@@ -29226,32 +29226,32 @@
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>Tìm truyện có yếu tố đông phương huyền huyễn và hệ thống</t>
+          <t>Tìm truyện có yếu tố đông phương huyền huyễn và hệ thống có trạng thái hoàn thành</t>
         </is>
       </c>
       <c r="C627" t="n">
         <v>6</v>
       </c>
       <c r="D627" t="n">
-        <v>14198</v>
+        <v>20650</v>
       </c>
       <c r="E627" t="inlineStr">
         <is>
-          <t>Vừa Thành Phong Hào Đấu La, Đạo Lữ Hệ Thống Tìm Tới Cửa! [Convert]</t>
+          <t>Vạn Lần Hoàn Trả, Lão Phu Tuổi Già Đi Làm Liếm Cẩu [Dịch]</t>
         </is>
       </c>
       <c r="F627" t="inlineStr">
         <is>
-          <t>Đồng Nhân</t>
+          <t>Huyền Huyễn</t>
         </is>
       </c>
       <c r="G627" t="inlineStr">
         <is>
-          <t>Đang ra</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="H627" t="n">
-        <v>6.4572</v>
+        <v>9.4217</v>
       </c>
       <c r="I627" t="inlineStr">
         <is>
@@ -29260,7 +29260,7 @@
       </c>
       <c r="J627" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/14198-vua-thanh-phong-hao-dau-la-dao-lu-he-thong-tim-toi-cua-convert</t>
+          <t>https://sitruyencv.com/story/20650-van-lan-hoan-tra-lao-phu-tuoi-gia-di-lam-liem-cau-dich</t>
         </is>
       </c>
     </row>
@@ -29272,23 +29272,23 @@
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>Tìm truyện có yếu tố đông phương huyền huyễn và hệ thống</t>
+          <t>Tìm truyện có yếu tố đông phương huyền huyễn và hệ thống có trạng thái hoàn thành</t>
         </is>
       </c>
       <c r="C628" t="n">
         <v>7</v>
       </c>
       <c r="D628" t="n">
-        <v>20776</v>
+        <v>19710</v>
       </c>
       <c r="E628" t="inlineStr">
         <is>
-          <t>Vạn Tộc Chiến Trường: Ta Có Hệ Thống Bạo Kích Hàng Tỷ Lần [Dịch]</t>
+          <t>Sau Ly Hôn, Họ Lại Theo Đuổi Tôi [Dịch]</t>
         </is>
       </c>
       <c r="F628" t="inlineStr">
         <is>
-          <t>Đô Thị, Võng Du, Hệ Thống</t>
+          <t>Đô Thị, Sủng</t>
         </is>
       </c>
       <c r="G628" t="inlineStr">
@@ -29297,7 +29297,7 @@
         </is>
       </c>
       <c r="H628" t="n">
-        <v>6.2785</v>
+        <v>9.271599999999999</v>
       </c>
       <c r="I628" t="inlineStr">
         <is>
@@ -29306,7 +29306,7 @@
       </c>
       <c r="J628" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/20776-van-toc-chien-truong-ta-co-he-thong-bao-kich-hang-ty-lan-dich</t>
+          <t>https://sitruyencv.com/story/19710-sau-ly-hon-ho-lai-theo-duoi-toi-dich</t>
         </is>
       </c>
     </row>
@@ -29318,32 +29318,32 @@
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>Tìm truyện có yếu tố đông phương huyền huyễn và hệ thống</t>
+          <t>Tìm truyện có yếu tố đông phương huyền huyễn và hệ thống có trạng thái hoàn thành</t>
         </is>
       </c>
       <c r="C629" t="n">
         <v>8</v>
       </c>
       <c r="D629" t="n">
-        <v>16100</v>
+        <v>5138</v>
       </c>
       <c r="E629" t="inlineStr">
         <is>
-          <t>Cao Võ: Ta Có Thể Hấp Thu Điểm Kinh Nghiệm [Convert]</t>
+          <t>Đánh Dấu Già Thiên Trăm Năm Thành Thánh [Convert]</t>
         </is>
       </c>
       <c r="F629" t="inlineStr">
         <is>
-          <t>Đô Thị</t>
+          <t>Huyền Huyễn</t>
         </is>
       </c>
       <c r="G629" t="inlineStr">
         <is>
-          <t>Đang ra</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="H629" t="n">
-        <v>6.0483</v>
+        <v>9.1229</v>
       </c>
       <c r="I629" t="inlineStr">
         <is>
@@ -29352,7 +29352,7 @@
       </c>
       <c r="J629" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/16100-cao-vo-ta-co-the-hap-thu-diem-kinh-nghiem-convert</t>
+          <t>https://sitruyencv.com/story/5138-danh-dau-gia-thien-tram-nam-thanh-thanh-convert</t>
         </is>
       </c>
     </row>
@@ -29364,18 +29364,18 @@
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>Tìm truyện có yếu tố đông phương huyền huyễn và hệ thống</t>
+          <t>Tìm truyện có yếu tố đông phương huyền huyễn và hệ thống có trạng thái hoàn thành</t>
         </is>
       </c>
       <c r="C630" t="n">
         <v>9</v>
       </c>
       <c r="D630" t="n">
-        <v>16838</v>
+        <v>17916</v>
       </c>
       <c r="E630" t="inlineStr">
         <is>
-          <t>Tu Tiên: Trùng Sinh Dị Giới Chế Tạo Tối Cường Tông Môn [Convert]</t>
+          <t>Từ Thiết Y Công Bắt Đầu Nhục Thân Thành Thánh [Convert]</t>
         </is>
       </c>
       <c r="F630" t="inlineStr">
@@ -29389,7 +29389,7 @@
         </is>
       </c>
       <c r="H630" t="n">
-        <v>5.9292</v>
+        <v>8.934699999999999</v>
       </c>
       <c r="I630" t="inlineStr">
         <is>
@@ -29398,7 +29398,7 @@
       </c>
       <c r="J630" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/16838-tu-tien-trung-sinh-di-gioi-che-tao-toi-cuong-tong-mon-convert</t>
+          <t>https://sitruyencv.com/story/17916-tu-thiet-y-cong-bat-dau-nhuc-than-thanh-thanh-convert</t>
         </is>
       </c>
     </row>
@@ -29410,18 +29410,18 @@
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>Tìm truyện có yếu tố đông phương huyền huyễn và hệ thống</t>
+          <t>Tìm truyện có yếu tố đông phương huyền huyễn và hệ thống có trạng thái hoàn thành</t>
         </is>
       </c>
       <c r="C631" t="n">
         <v>10</v>
       </c>
       <c r="D631" t="n">
-        <v>10180</v>
+        <v>17533</v>
       </c>
       <c r="E631" t="inlineStr">
         <is>
-          <t>Nhà Ta Nương Tử , Không Thích Hợp [Convert]</t>
+          <t>Vô Địch Theo Cướp Đoạt Khí Huyết Bắt Đầu [Convert]</t>
         </is>
       </c>
       <c r="F631" t="inlineStr">
@@ -29435,7 +29435,7 @@
         </is>
       </c>
       <c r="H631" t="n">
-        <v>5.7987</v>
+        <v>8.611499999999999</v>
       </c>
       <c r="I631" t="inlineStr">
         <is>
@@ -29444,7 +29444,7 @@
       </c>
       <c r="J631" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/10180-nha-ta-nuong-tu-khong-thich-hop-convert</t>
+          <t>https://sitruyencv.com/story/17533-vo-dich-theo-cuop-doat-khi-huyet-bat-dau-convert</t>
         </is>
       </c>
     </row>
@@ -29456,18 +29456,18 @@
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>Tìm truyện có yếu tố huyễn tưởng tu tiên và hệ thống</t>
+          <t>Tìm truyện có yếu tố huyễn tưởng tu tiên và hệ thống có hơn 500 chương truyện</t>
         </is>
       </c>
       <c r="C632" t="n">
         <v>1</v>
       </c>
       <c r="D632" t="n">
-        <v>19982</v>
+        <v>13674</v>
       </c>
       <c r="E632" t="inlineStr">
         <is>
-          <t>Gia Tộc Tu Tiên: Ta Lấy Luân Hồi Chuyển Thế Tìm Trường Sinh [Convert]</t>
+          <t>Vạn Thú Thế Gia Quật Khởi [Convert]</t>
         </is>
       </c>
       <c r="F632" t="inlineStr">
@@ -29481,7 +29481,7 @@
         </is>
       </c>
       <c r="H632" t="n">
-        <v>12.588</v>
+        <v>15.3955</v>
       </c>
       <c r="I632" t="inlineStr">
         <is>
@@ -29490,7 +29490,7 @@
       </c>
       <c r="J632" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/19982-gia-toc-tu-tien-ta-lay-luan-hoi-chuyen-the-tim-truong-sinh-convert</t>
+          <t>https://sitruyencv.com/story/13674-van-thu-the-gia-quat-khoi-convert</t>
         </is>
       </c>
     </row>
@@ -29502,23 +29502,23 @@
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>Tìm truyện có yếu tố huyễn tưởng tu tiên và hệ thống</t>
+          <t>Tìm truyện có yếu tố huyễn tưởng tu tiên và hệ thống có hơn 500 chương truyện</t>
         </is>
       </c>
       <c r="C633" t="n">
         <v>2</v>
       </c>
       <c r="D633" t="n">
-        <v>19710</v>
+        <v>19982</v>
       </c>
       <c r="E633" t="inlineStr">
         <is>
-          <t>Sau Ly Hôn, Họ Lại Theo Đuổi Tôi [Dịch]</t>
+          <t>Gia Tộc Tu Tiên: Ta Lấy Luân Hồi Chuyển Thế Tìm Trường Sinh [Convert]</t>
         </is>
       </c>
       <c r="F633" t="inlineStr">
         <is>
-          <t>Đô Thị, Sủng</t>
+          <t>Tiên Hiệp</t>
         </is>
       </c>
       <c r="G633" t="inlineStr">
@@ -29527,7 +29527,7 @@
         </is>
       </c>
       <c r="H633" t="n">
-        <v>9.9079</v>
+        <v>12.588</v>
       </c>
       <c r="I633" t="inlineStr">
         <is>
@@ -29536,7 +29536,7 @@
       </c>
       <c r="J633" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/19710-sau-ly-hon-ho-lai-theo-duoi-toi-dich</t>
+          <t>https://sitruyencv.com/story/19982-gia-toc-tu-tien-ta-lay-luan-hoi-chuyen-the-tim-truong-sinh-convert</t>
         </is>
       </c>
     </row>
@@ -29548,23 +29548,23 @@
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>Tìm truyện có yếu tố huyễn tưởng tu tiên và hệ thống</t>
+          <t>Tìm truyện có yếu tố huyễn tưởng tu tiên và hệ thống có hơn 500 chương truyện</t>
         </is>
       </c>
       <c r="C634" t="n">
         <v>3</v>
       </c>
       <c r="D634" t="n">
-        <v>14198</v>
+        <v>19710</v>
       </c>
       <c r="E634" t="inlineStr">
         <is>
-          <t>Vừa Thành Phong Hào Đấu La, Đạo Lữ Hệ Thống Tìm Tới Cửa! [Convert]</t>
+          <t>Sau Ly Hôn, Họ Lại Theo Đuổi Tôi [Dịch]</t>
         </is>
       </c>
       <c r="F634" t="inlineStr">
         <is>
-          <t>Đồng Nhân</t>
+          <t>Đô Thị, Sủng</t>
         </is>
       </c>
       <c r="G634" t="inlineStr">
@@ -29573,7 +29573,7 @@
         </is>
       </c>
       <c r="H634" t="n">
-        <v>9.217000000000001</v>
+        <v>9.9079</v>
       </c>
       <c r="I634" t="inlineStr">
         <is>
@@ -29582,7 +29582,7 @@
       </c>
       <c r="J634" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/14198-vua-thanh-phong-hao-dau-la-dao-lu-he-thong-tim-toi-cua-convert</t>
+          <t>https://sitruyencv.com/story/19710-sau-ly-hon-ho-lai-theo-duoi-toi-dich</t>
         </is>
       </c>
     </row>
@@ -29594,23 +29594,23 @@
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>Tìm truyện có yếu tố huyễn tưởng tu tiên và hệ thống</t>
+          <t>Tìm truyện có yếu tố huyễn tưởng tu tiên và hệ thống có hơn 500 chương truyện</t>
         </is>
       </c>
       <c r="C635" t="n">
         <v>4</v>
       </c>
       <c r="D635" t="n">
-        <v>10730</v>
+        <v>9529</v>
       </c>
       <c r="E635" t="inlineStr">
         <is>
-          <t>Bắt Đầu Bất Hủ Đại Đế, Chế Tạo Vạn Cổ Tiên Tông [Convert]</t>
+          <t>Trực Tiếp Thiết Kế Tử Vong [Convert]</t>
         </is>
       </c>
       <c r="F635" t="inlineStr">
         <is>
-          <t>Huyền Huyễn</t>
+          <t>Đô Thị</t>
         </is>
       </c>
       <c r="G635" t="inlineStr">
@@ -29619,7 +29619,7 @@
         </is>
       </c>
       <c r="H635" t="n">
-        <v>8.272</v>
+        <v>9.462899999999999</v>
       </c>
       <c r="I635" t="inlineStr">
         <is>
@@ -29628,7 +29628,7 @@
       </c>
       <c r="J635" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/10730-bat-dau-bat-hu-dai-de-che-tao-van-co-tien-tong-convert</t>
+          <t>https://sitruyencv.com/story/9529-truc-tiep-thiet-ke-tu-vong-convert</t>
         </is>
       </c>
     </row>
@@ -29640,23 +29640,23 @@
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>Tìm truyện có yếu tố huyễn tưởng tu tiên và hệ thống</t>
+          <t>Tìm truyện có yếu tố huyễn tưởng tu tiên và hệ thống có hơn 500 chương truyện</t>
         </is>
       </c>
       <c r="C636" t="n">
         <v>5</v>
       </c>
       <c r="D636" t="n">
-        <v>19317</v>
+        <v>19395</v>
       </c>
       <c r="E636" t="inlineStr">
         <is>
-          <t>Kinh Hồng [Dịch]</t>
+          <t>Trong Thôn Có Một Tu Tiên Tông Môn [Convert]</t>
         </is>
       </c>
       <c r="F636" t="inlineStr">
         <is>
-          <t>Tiên Hiệp, Huyền Huyễn, Lịch Sử Quân Sự, Cổ Đại, Tiên Hiệp Kỳ Duyên, Cổ Đại Ngôn Tình</t>
+          <t>Tiên Hiệp</t>
         </is>
       </c>
       <c r="G636" t="inlineStr">
@@ -29665,7 +29665,7 @@
         </is>
       </c>
       <c r="H636" t="n">
-        <v>7.1017</v>
+        <v>9.329700000000001</v>
       </c>
       <c r="I636" t="inlineStr">
         <is>
@@ -29674,7 +29674,7 @@
       </c>
       <c r="J636" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/19317-kinh-hong-dich</t>
+          <t>https://sitruyencv.com/story/19395-trong-thon-co-mot-tu-tien-tong-mon-convert</t>
         </is>
       </c>
     </row>
@@ -29686,23 +29686,23 @@
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>Tìm truyện có yếu tố huyễn tưởng tu tiên và hệ thống</t>
+          <t>Tìm truyện có yếu tố huyễn tưởng tu tiên và hệ thống có hơn 500 chương truyện</t>
         </is>
       </c>
       <c r="C637" t="n">
         <v>6</v>
       </c>
       <c r="D637" t="n">
-        <v>19992</v>
+        <v>14198</v>
       </c>
       <c r="E637" t="inlineStr">
         <is>
-          <t>Trường Sinh Tu Tiên, Từ Thục Năng Sinh Xảo Bắt Đầu [Convert]</t>
+          <t>Vừa Thành Phong Hào Đấu La, Đạo Lữ Hệ Thống Tìm Tới Cửa! [Convert]</t>
         </is>
       </c>
       <c r="F637" t="inlineStr">
         <is>
-          <t>Tiên Hiệp</t>
+          <t>Đồng Nhân</t>
         </is>
       </c>
       <c r="G637" t="inlineStr">
@@ -29711,7 +29711,7 @@
         </is>
       </c>
       <c r="H637" t="n">
-        <v>7.0202</v>
+        <v>9.217000000000001</v>
       </c>
       <c r="I637" t="inlineStr">
         <is>
@@ -29720,7 +29720,7 @@
       </c>
       <c r="J637" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/19992-truong-sinh-tu-tien-tu-thuc-nang-sinh-xao-bat-dau-convert</t>
+          <t>https://sitruyencv.com/story/14198-vua-thanh-phong-hao-dau-la-dao-lu-he-thong-tim-toi-cua-convert</t>
         </is>
       </c>
     </row>
@@ -29732,32 +29732,32 @@
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>Tìm truyện có yếu tố huyễn tưởng tu tiên và hệ thống</t>
+          <t>Tìm truyện có yếu tố huyễn tưởng tu tiên và hệ thống có hơn 500 chương truyện</t>
         </is>
       </c>
       <c r="C638" t="n">
         <v>7</v>
       </c>
       <c r="D638" t="n">
-        <v>20034</v>
+        <v>10730</v>
       </c>
       <c r="E638" t="inlineStr">
         <is>
-          <t>Quyển Không Nổi Nữa, Để Ta Đi Ngoại Môn Đi [Convert]</t>
+          <t>Bắt Đầu Bất Hủ Đại Đế, Chế Tạo Vạn Cổ Tiên Tông [Convert]</t>
         </is>
       </c>
       <c r="F638" t="inlineStr">
         <is>
-          <t>Tiên Hiệp</t>
+          <t>Huyền Huyễn</t>
         </is>
       </c>
       <c r="G638" t="inlineStr">
         <is>
-          <t>Đang ra</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="H638" t="n">
-        <v>6.9307</v>
+        <v>8.272</v>
       </c>
       <c r="I638" t="inlineStr">
         <is>
@@ -29766,7 +29766,7 @@
       </c>
       <c r="J638" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/20034-quyen-khong-noi-nua-de-ta-di-ngoai-mon-di-convert</t>
+          <t>https://sitruyencv.com/story/10730-bat-dau-bat-hu-dai-de-che-tao-van-co-tien-tong-convert</t>
         </is>
       </c>
     </row>
@@ -29778,18 +29778,18 @@
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>Tìm truyện có yếu tố huyễn tưởng tu tiên và hệ thống</t>
+          <t>Tìm truyện có yếu tố huyễn tưởng tu tiên và hệ thống có hơn 500 chương truyện</t>
         </is>
       </c>
       <c r="C639" t="n">
         <v>8</v>
       </c>
       <c r="D639" t="n">
-        <v>19395</v>
+        <v>13524</v>
       </c>
       <c r="E639" t="inlineStr">
         <is>
-          <t>Trong Thôn Có Một Tu Tiên Tông Môn [Convert]</t>
+          <t>Lôi Linh Căn Tu Tiên, Ta Có Gấp 10 Lần Phục Chế Không Gian [Convert]</t>
         </is>
       </c>
       <c r="F639" t="inlineStr">
@@ -29803,7 +29803,7 @@
         </is>
       </c>
       <c r="H639" t="n">
-        <v>6.8623</v>
+        <v>7.7964</v>
       </c>
       <c r="I639" t="inlineStr">
         <is>
@@ -29812,7 +29812,7 @@
       </c>
       <c r="J639" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/19395-trong-thon-co-mot-tu-tien-tong-mon-convert</t>
+          <t>https://sitruyencv.com/story/13524-loi-linh-can-tu-tien-ta-co-gap-10-lan-phuc-che-khong-gian-convert</t>
         </is>
       </c>
     </row>
@@ -29824,32 +29824,32 @@
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>Tìm truyện có yếu tố huyễn tưởng tu tiên và hệ thống</t>
+          <t>Tìm truyện có yếu tố huyễn tưởng tu tiên và hệ thống có hơn 500 chương truyện</t>
         </is>
       </c>
       <c r="C640" t="n">
         <v>9</v>
       </c>
       <c r="D640" t="n">
-        <v>18746</v>
+        <v>16838</v>
       </c>
       <c r="E640" t="inlineStr">
         <is>
-          <t>Kinh Dị Nhạc Viên [Convert]</t>
+          <t>Tu Tiên: Trùng Sinh Dị Giới Chế Tạo Tối Cường Tông Môn [Convert]</t>
         </is>
       </c>
       <c r="F640" t="inlineStr">
         <is>
-          <t>Huyền Nghi, Hệ Thống, Dị Năng, Linh Dị, Trinh Thám, Huyền Nghi Thần Quái</t>
+          <t>Huyền Huyễn</t>
         </is>
       </c>
       <c r="G640" t="inlineStr">
         <is>
-          <t>Hoàn thành</t>
+          <t>Đang ra</t>
         </is>
       </c>
       <c r="H640" t="n">
-        <v>6.7607</v>
+        <v>7.4857</v>
       </c>
       <c r="I640" t="inlineStr">
         <is>
@@ -29858,7 +29858,7 @@
       </c>
       <c r="J640" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/18746-kinh-di-nhac-vien-convert</t>
+          <t>https://sitruyencv.com/story/16838-tu-tien-trung-sinh-di-gioi-che-tao-toi-cuong-tong-mon-convert</t>
         </is>
       </c>
     </row>
@@ -29870,32 +29870,32 @@
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>Tìm truyện có yếu tố huyễn tưởng tu tiên và hệ thống</t>
+          <t>Tìm truyện có yếu tố huyễn tưởng tu tiên và hệ thống có hơn 500 chương truyện</t>
         </is>
       </c>
       <c r="C641" t="n">
         <v>10</v>
       </c>
       <c r="D641" t="n">
-        <v>19111</v>
+        <v>16201</v>
       </c>
       <c r="E641" t="inlineStr">
         <is>
-          <t>Người Ở Tu Tiên Giới, Lại Cho Ta Hệ Thống Đô Thị Thần Hào? [Convert]</t>
+          <t>Nữ Hiệp Xin Dừng Tay [Convert]</t>
         </is>
       </c>
       <c r="F641" t="inlineStr">
         <is>
-          <t>Tiên Hiệp</t>
+          <t>Dã Sử</t>
         </is>
       </c>
       <c r="G641" t="inlineStr">
         <is>
-          <t>Đang ra</t>
+          <t>Tạm dừng</t>
         </is>
       </c>
       <c r="H641" t="n">
-        <v>6.6312</v>
+        <v>7.2004</v>
       </c>
       <c r="I641" t="inlineStr">
         <is>
@@ -29904,7 +29904,7 @@
       </c>
       <c r="J641" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/19111-nguoi-o-tu-tien-gioi-lai-cho-ta-he-thong-do-thi-than-hao-convert</t>
+          <t>https://sitruyencv.com/story/16201-nu-hiep-xin-dung-tay-convert</t>
         </is>
       </c>
     </row>
@@ -29916,7 +29916,7 @@
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>Tìm truyện có yếu tố chư thiên vạn giới và hệ thống</t>
+          <t>Tìm truyện có yếu tố chư thiên vạn giới và hệ thống có trạng thái đang ra</t>
         </is>
       </c>
       <c r="C642" t="n">
@@ -29941,7 +29941,7 @@
         </is>
       </c>
       <c r="H642" t="n">
-        <v>11.8697</v>
+        <v>14.1241</v>
       </c>
       <c r="I642" t="inlineStr">
         <is>
@@ -29962,32 +29962,32 @@
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>Tìm truyện có yếu tố chư thiên vạn giới và hệ thống</t>
+          <t>Tìm truyện có yếu tố chư thiên vạn giới và hệ thống có trạng thái đang ra</t>
         </is>
       </c>
       <c r="C643" t="n">
         <v>2</v>
       </c>
       <c r="D643" t="n">
-        <v>18746</v>
+        <v>19710</v>
       </c>
       <c r="E643" t="inlineStr">
         <is>
-          <t>Kinh Dị Nhạc Viên [Convert]</t>
+          <t>Sau Ly Hôn, Họ Lại Theo Đuổi Tôi [Dịch]</t>
         </is>
       </c>
       <c r="F643" t="inlineStr">
         <is>
-          <t>Huyền Nghi, Hệ Thống, Dị Năng, Linh Dị, Trinh Thám, Huyền Nghi Thần Quái</t>
+          <t>Đô Thị, Sủng</t>
         </is>
       </c>
       <c r="G643" t="inlineStr">
         <is>
-          <t>Hoàn thành</t>
+          <t>Đang ra</t>
         </is>
       </c>
       <c r="H643" t="n">
-        <v>10.2926</v>
+        <v>12.628</v>
       </c>
       <c r="I643" t="inlineStr">
         <is>
@@ -29996,7 +29996,7 @@
       </c>
       <c r="J643" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/18746-kinh-di-nhac-vien-convert</t>
+          <t>https://sitruyencv.com/story/19710-sau-ly-hon-ho-lai-theo-duoi-toi-dich</t>
         </is>
       </c>
     </row>
@@ -30008,23 +30008,23 @@
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>Tìm truyện có yếu tố chư thiên vạn giới và hệ thống</t>
+          <t>Tìm truyện có yếu tố chư thiên vạn giới và hệ thống có trạng thái đang ra</t>
         </is>
       </c>
       <c r="C644" t="n">
         <v>3</v>
       </c>
       <c r="D644" t="n">
-        <v>19982</v>
+        <v>11553</v>
       </c>
       <c r="E644" t="inlineStr">
         <is>
-          <t>Gia Tộc Tu Tiên: Ta Lấy Luân Hồi Chuyển Thế Tìm Trường Sinh [Convert]</t>
+          <t>Bắt Đầu Kém Chút Bị Ăn, May Mắn Ta Có Thể Dời Đi Mặt Trái Trạng Thái [Convert]</t>
         </is>
       </c>
       <c r="F644" t="inlineStr">
         <is>
-          <t>Tiên Hiệp</t>
+          <t>Huyền Huyễn</t>
         </is>
       </c>
       <c r="G644" t="inlineStr">
@@ -30033,7 +30033,7 @@
         </is>
       </c>
       <c r="H644" t="n">
-        <v>9.558</v>
+        <v>11.8313</v>
       </c>
       <c r="I644" t="inlineStr">
         <is>
@@ -30042,7 +30042,7 @@
       </c>
       <c r="J644" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/19982-gia-toc-tu-tien-ta-lay-luan-hoi-chuyen-the-tim-truong-sinh-convert</t>
+          <t>https://sitruyencv.com/story/11553-bat-dau-kem-chut-bi-an-may-man-ta-co-the-doi-di-mat-trai-trang-thai-convert</t>
         </is>
       </c>
     </row>
@@ -30054,32 +30054,32 @@
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>Tìm truyện có yếu tố chư thiên vạn giới và hệ thống</t>
+          <t>Tìm truyện có yếu tố chư thiên vạn giới và hệ thống có trạng thái đang ra</t>
         </is>
       </c>
       <c r="C645" t="n">
         <v>4</v>
       </c>
       <c r="D645" t="n">
-        <v>19710</v>
+        <v>20392</v>
       </c>
       <c r="E645" t="inlineStr">
         <is>
-          <t>Sau Ly Hôn, Họ Lại Theo Đuổi Tôi [Dịch]</t>
+          <t>Nhà Ta Thế Hệ Cường Đạo, Tiểu Tử Ngươi Thi Đậu Trạng Nguyên [Dịch]</t>
         </is>
       </c>
       <c r="F645" t="inlineStr">
         <is>
-          <t>Đô Thị, Sủng</t>
+          <t>Huyền Huyễn, Cổ Đại</t>
         </is>
       </c>
       <c r="G645" t="inlineStr">
         <is>
-          <t>Đang ra</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="H645" t="n">
-        <v>9.4641</v>
+        <v>11.6214</v>
       </c>
       <c r="I645" t="inlineStr">
         <is>
@@ -30088,7 +30088,7 @@
       </c>
       <c r="J645" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/19710-sau-ly-hon-ho-lai-theo-duoi-toi-dich</t>
+          <t>https://sitruyencv.com/story/20392-nha-ta-the-he-cuong-dao-tieu-tu-nguoi-thi-dau-trang-nguyen-dich</t>
         </is>
       </c>
     </row>
@@ -30100,23 +30100,23 @@
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>Tìm truyện có yếu tố chư thiên vạn giới và hệ thống</t>
+          <t>Tìm truyện có yếu tố chư thiên vạn giới và hệ thống có trạng thái đang ra</t>
         </is>
       </c>
       <c r="C646" t="n">
         <v>5</v>
       </c>
       <c r="D646" t="n">
-        <v>15905</v>
+        <v>18959</v>
       </c>
       <c r="E646" t="inlineStr">
         <is>
-          <t>Toàn Dân Đầu Tư Thời Đại: Chỉ Có Ta Biết Nhân Vật Chính [Convert]</t>
+          <t>Ta Thiên Đình Thái Tử Gia, Thiên Đế Cha Vô Địch, Ta Nằm [Convert]</t>
         </is>
       </c>
       <c r="F646" t="inlineStr">
         <is>
-          <t>Huyền Huyễn</t>
+          <t>Tiên Hiệp, Huyền Huyễn, Hệ Thống</t>
         </is>
       </c>
       <c r="G646" t="inlineStr">
@@ -30125,7 +30125,7 @@
         </is>
       </c>
       <c r="H646" t="n">
-        <v>8.339700000000001</v>
+        <v>11.0676</v>
       </c>
       <c r="I646" t="inlineStr">
         <is>
@@ -30134,7 +30134,7 @@
       </c>
       <c r="J646" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/15905-toan-dan-dau-tu-thoi-dai-chi-co-ta-biet-nhan-vat-chinh-convert</t>
+          <t>https://sitruyencv.com/story/18959-ta-thien-dinh-thai-tu-gia-thien-de-cha-vo-dich-ta-nam-convert</t>
         </is>
       </c>
     </row>
@@ -30146,23 +30146,23 @@
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>Tìm truyện có yếu tố chư thiên vạn giới và hệ thống</t>
+          <t>Tìm truyện có yếu tố chư thiên vạn giới và hệ thống có trạng thái đang ra</t>
         </is>
       </c>
       <c r="C647" t="n">
         <v>6</v>
       </c>
       <c r="D647" t="n">
-        <v>19729</v>
+        <v>18746</v>
       </c>
       <c r="E647" t="inlineStr">
         <is>
-          <t>Đấu La: Thu Phục Nữ Thần [Dịch]</t>
+          <t>Kinh Dị Nhạc Viên [Convert]</t>
         </is>
       </c>
       <c r="F647" t="inlineStr">
         <is>
-          <t>Huyền Huyễn, Đồng Nhân, Hệ Thống, Phản Phái, Dị Giới, Sủng</t>
+          <t>Huyền Nghi, Hệ Thống, Dị Năng, Linh Dị, Trinh Thám, Huyền Nghi Thần Quái</t>
         </is>
       </c>
       <c r="G647" t="inlineStr">
@@ -30171,7 +30171,7 @@
         </is>
       </c>
       <c r="H647" t="n">
-        <v>8.3361</v>
+        <v>10.2926</v>
       </c>
       <c r="I647" t="inlineStr">
         <is>
@@ -30180,7 +30180,7 @@
       </c>
       <c r="J647" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/19729-dau-la-thu-phuc-nu-than-dich</t>
+          <t>https://sitruyencv.com/story/18746-kinh-di-nhac-vien-convert</t>
         </is>
       </c>
     </row>
@@ -30192,18 +30192,18 @@
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>Tìm truyện có yếu tố chư thiên vạn giới và hệ thống</t>
+          <t>Tìm truyện có yếu tố chư thiên vạn giới và hệ thống có trạng thái đang ra</t>
         </is>
       </c>
       <c r="C648" t="n">
         <v>7</v>
       </c>
       <c r="D648" t="n">
-        <v>18885</v>
+        <v>17365</v>
       </c>
       <c r="E648" t="inlineStr">
         <is>
-          <t>Chiến Thần Cuồng Tiêu Chi Chư Thiên Vạn Giới [Convert]</t>
+          <t>Ta Có Một Gốc Thần Thoại Thụ [Convert]</t>
         </is>
       </c>
       <c r="F648" t="inlineStr">
@@ -30217,7 +30217,7 @@
         </is>
       </c>
       <c r="H648" t="n">
-        <v>8.188599999999999</v>
+        <v>9.812099999999999</v>
       </c>
       <c r="I648" t="inlineStr">
         <is>
@@ -30226,7 +30226,7 @@
       </c>
       <c r="J648" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/18885-chien-than-cuong-tieu-chi-chu-thien-van-gioi-convert</t>
+          <t>https://sitruyencv.com/story/17365-ta-co-mot-goc-than-thoai-thu-convert</t>
         </is>
       </c>
     </row>
@@ -30238,23 +30238,23 @@
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>Tìm truyện có yếu tố chư thiên vạn giới và hệ thống</t>
+          <t>Tìm truyện có yếu tố chư thiên vạn giới và hệ thống có trạng thái đang ra</t>
         </is>
       </c>
       <c r="C649" t="n">
         <v>8</v>
       </c>
       <c r="D649" t="n">
-        <v>14198</v>
+        <v>13623</v>
       </c>
       <c r="E649" t="inlineStr">
         <is>
-          <t>Vừa Thành Phong Hào Đấu La, Đạo Lữ Hệ Thống Tìm Tới Cửa! [Convert]</t>
+          <t>Cái Gì Phản Phái Nam Phụ, Rõ Ràng Là Sư Huynh Ấm Áp! [Convert]</t>
         </is>
       </c>
       <c r="F649" t="inlineStr">
         <is>
-          <t>Đồng Nhân</t>
+          <t>Huyền Huyễn</t>
         </is>
       </c>
       <c r="G649" t="inlineStr">
@@ -30263,7 +30263,7 @@
         </is>
       </c>
       <c r="H649" t="n">
-        <v>8.123100000000001</v>
+        <v>9.684799999999999</v>
       </c>
       <c r="I649" t="inlineStr">
         <is>
@@ -30272,7 +30272,7 @@
       </c>
       <c r="J649" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/14198-vua-thanh-phong-hao-dau-la-dao-lu-he-thong-tim-toi-cua-convert</t>
+          <t>https://sitruyencv.com/story/13623-cai-gi-phan-phai-nam-phu-ro-rang-la-su-huynh-am-ap-convert</t>
         </is>
       </c>
     </row>
@@ -30284,23 +30284,23 @@
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>Tìm truyện có yếu tố chư thiên vạn giới và hệ thống</t>
+          <t>Tìm truyện có yếu tố chư thiên vạn giới và hệ thống có trạng thái đang ra</t>
         </is>
       </c>
       <c r="C650" t="n">
         <v>9</v>
       </c>
       <c r="D650" t="n">
-        <v>18959</v>
+        <v>19982</v>
       </c>
       <c r="E650" t="inlineStr">
         <is>
-          <t>Ta Thiên Đình Thái Tử Gia, Thiên Đế Cha Vô Địch, Ta Nằm [Convert]</t>
+          <t>Gia Tộc Tu Tiên: Ta Lấy Luân Hồi Chuyển Thế Tìm Trường Sinh [Convert]</t>
         </is>
       </c>
       <c r="F650" t="inlineStr">
         <is>
-          <t>Tiên Hiệp, Huyền Huyễn, Hệ Thống</t>
+          <t>Tiên Hiệp</t>
         </is>
       </c>
       <c r="G650" t="inlineStr">
@@ -30309,7 +30309,7 @@
         </is>
       </c>
       <c r="H650" t="n">
-        <v>7.9562</v>
+        <v>9.558</v>
       </c>
       <c r="I650" t="inlineStr">
         <is>
@@ -30318,7 +30318,7 @@
       </c>
       <c r="J650" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/18959-ta-thien-dinh-thai-tu-gia-thien-de-cha-vo-dich-ta-nam-convert</t>
+          <t>https://sitruyencv.com/story/19982-gia-toc-tu-tien-ta-lay-luan-hoi-chuyen-the-tim-truong-sinh-convert</t>
         </is>
       </c>
     </row>
@@ -30330,32 +30330,32 @@
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>Tìm truyện có yếu tố chư thiên vạn giới và hệ thống</t>
+          <t>Tìm truyện có yếu tố chư thiên vạn giới và hệ thống có trạng thái đang ra</t>
         </is>
       </c>
       <c r="C651" t="n">
         <v>10</v>
       </c>
       <c r="D651" t="n">
-        <v>15086</v>
+        <v>1097</v>
       </c>
       <c r="E651" t="inlineStr">
         <is>
-          <t>Hải Tặc: Ta, Rocks Trên Thuyền Chiến Lực Mạnh Nhất [Convert]</t>
+          <t>Bắt Đầu Bị Trục Xuất Vương Phủ: Triệu Hoán Tuyết Đại Long Kỵ [Convert]</t>
         </is>
       </c>
       <c r="F651" t="inlineStr">
         <is>
-          <t>Đồng Nhân</t>
+          <t>Dã Sử</t>
         </is>
       </c>
       <c r="G651" t="inlineStr">
         <is>
-          <t>Đang ra</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="H651" t="n">
-        <v>7.6521</v>
+        <v>9.4773</v>
       </c>
       <c r="I651" t="inlineStr">
         <is>
@@ -30364,7 +30364,7 @@
       </c>
       <c r="J651" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/15086-hai-tac-ta-rocks-tren-thuyen-chien-luc-manh-nhat-convert</t>
+          <t>https://sitruyencv.com/story/1097-bat-dau-bi-truc-xuat-vuong-phu-trieu-hoan-tuyet-dai-long-ky-convert</t>
         </is>
       </c>
     </row>
@@ -38196,7 +38196,7 @@
       </c>
       <c r="B822" t="inlineStr">
         <is>
-          <t>Tìm truyện mà vừa có hệ thống vừa phát triển thế lực và main cơ trí.</t>
+          <t>Tìm truyện mà vừa có hệ thống vừa phát triển thế lực, main cơ trí và có trạng thái đang ra</t>
         </is>
       </c>
       <c r="C822" t="n">
@@ -38221,7 +38221,7 @@
         </is>
       </c>
       <c r="H822" t="n">
-        <v>18.0859</v>
+        <v>18.2824</v>
       </c>
       <c r="I822" t="inlineStr">
         <is>
@@ -38242,23 +38242,23 @@
       </c>
       <c r="B823" t="inlineStr">
         <is>
-          <t>Tìm truyện mà vừa có hệ thống vừa phát triển thế lực và main cơ trí.</t>
+          <t>Tìm truyện mà vừa có hệ thống vừa phát triển thế lực, main cơ trí và có trạng thái đang ra</t>
         </is>
       </c>
       <c r="C823" t="n">
         <v>2</v>
       </c>
       <c r="D823" t="n">
-        <v>17802</v>
+        <v>11553</v>
       </c>
       <c r="E823" t="inlineStr">
         <is>
-          <t>Lớp Cầu Sinh: Ta Mang Nữ Đồng Học Khai Chi Tán Diệp [Convert]</t>
+          <t>Bắt Đầu Kém Chút Bị Ăn, May Mắn Ta Có Thể Dời Đi Mặt Trái Trạng Thái [Convert]</t>
         </is>
       </c>
       <c r="F823" t="inlineStr">
         <is>
-          <t>Đô Thị</t>
+          <t>Huyền Huyễn</t>
         </is>
       </c>
       <c r="G823" t="inlineStr">
@@ -38267,7 +38267,7 @@
         </is>
       </c>
       <c r="H823" t="n">
-        <v>13.1144</v>
+        <v>16.8027</v>
       </c>
       <c r="I823" t="inlineStr">
         <is>
@@ -38276,7 +38276,7 @@
       </c>
       <c r="J823" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/17802-lop-cau-sinh-ta-mang-nu-dong-hoc-khai-chi-tan-diep-convert</t>
+          <t>https://sitruyencv.com/story/11553-bat-dau-kem-chut-bi-an-may-man-ta-co-the-doi-di-mat-trai-trang-thai-convert</t>
         </is>
       </c>
     </row>
@@ -38288,7 +38288,7 @@
       </c>
       <c r="B824" t="inlineStr">
         <is>
-          <t>Tìm truyện mà vừa có hệ thống vừa phát triển thế lực và main cơ trí.</t>
+          <t>Tìm truyện mà vừa có hệ thống vừa phát triển thế lực, main cơ trí và có trạng thái đang ra</t>
         </is>
       </c>
       <c r="C824" t="n">
@@ -38313,7 +38313,7 @@
         </is>
       </c>
       <c r="H824" t="n">
-        <v>12.0827</v>
+        <v>15.5688</v>
       </c>
       <c r="I824" t="inlineStr">
         <is>
@@ -38334,23 +38334,23 @@
       </c>
       <c r="B825" t="inlineStr">
         <is>
-          <t>Tìm truyện mà vừa có hệ thống vừa phát triển thế lực và main cơ trí.</t>
+          <t>Tìm truyện mà vừa có hệ thống vừa phát triển thế lực, main cơ trí và có trạng thái đang ra</t>
         </is>
       </c>
       <c r="C825" t="n">
         <v>4</v>
       </c>
       <c r="D825" t="n">
-        <v>13514</v>
+        <v>17802</v>
       </c>
       <c r="E825" t="inlineStr">
         <is>
-          <t>Mạnh Nhất Gia Tộc, Từ Khai Chi Tán Diệp Bắt Đầu [Convert]</t>
+          <t>Lớp Cầu Sinh: Ta Mang Nữ Đồng Học Khai Chi Tán Diệp [Convert]</t>
         </is>
       </c>
       <c r="F825" t="inlineStr">
         <is>
-          <t>Huyền Huyễn</t>
+          <t>Đô Thị</t>
         </is>
       </c>
       <c r="G825" t="inlineStr">
@@ -38359,7 +38359,7 @@
         </is>
       </c>
       <c r="H825" t="n">
-        <v>11.2198</v>
+        <v>14.161</v>
       </c>
       <c r="I825" t="inlineStr">
         <is>
@@ -38368,7 +38368,7 @@
       </c>
       <c r="J825" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/13514-manh-nhat-gia-toc-tu-khai-chi-tan-diep-bat-dau-convert</t>
+          <t>https://sitruyencv.com/story/17802-lop-cau-sinh-ta-mang-nu-dong-hoc-khai-chi-tan-diep-convert</t>
         </is>
       </c>
     </row>
@@ -38380,23 +38380,23 @@
       </c>
       <c r="B826" t="inlineStr">
         <is>
-          <t>Tìm truyện mà vừa có hệ thống vừa phát triển thế lực và main cơ trí.</t>
+          <t>Tìm truyện mà vừa có hệ thống vừa phát triển thế lực, main cơ trí và có trạng thái đang ra</t>
         </is>
       </c>
       <c r="C826" t="n">
         <v>5</v>
       </c>
       <c r="D826" t="n">
-        <v>13674</v>
+        <v>13623</v>
       </c>
       <c r="E826" t="inlineStr">
         <is>
-          <t>Vạn Thú Thế Gia Quật Khởi [Convert]</t>
+          <t>Cái Gì Phản Phái Nam Phụ, Rõ Ràng Là Sư Huynh Ấm Áp! [Convert]</t>
         </is>
       </c>
       <c r="F826" t="inlineStr">
         <is>
-          <t>Tiên Hiệp</t>
+          <t>Huyền Huyễn</t>
         </is>
       </c>
       <c r="G826" t="inlineStr">
@@ -38405,7 +38405,7 @@
         </is>
       </c>
       <c r="H826" t="n">
-        <v>11.1012</v>
+        <v>13.267</v>
       </c>
       <c r="I826" t="inlineStr">
         <is>
@@ -38414,7 +38414,7 @@
       </c>
       <c r="J826" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/13674-van-thu-the-gia-quat-khoi-convert</t>
+          <t>https://sitruyencv.com/story/13623-cai-gi-phan-phai-nam-phu-ro-rang-la-su-huynh-am-ap-convert</t>
         </is>
       </c>
     </row>
@@ -38426,23 +38426,23 @@
       </c>
       <c r="B827" t="inlineStr">
         <is>
-          <t>Tìm truyện mà vừa có hệ thống vừa phát triển thế lực và main cơ trí.</t>
+          <t>Tìm truyện mà vừa có hệ thống vừa phát triển thế lực, main cơ trí và có trạng thái đang ra</t>
         </is>
       </c>
       <c r="C827" t="n">
         <v>6</v>
       </c>
       <c r="D827" t="n">
-        <v>19676</v>
+        <v>19019</v>
       </c>
       <c r="E827" t="inlineStr">
         <is>
-          <t>Tận Thế Phản Phái: Bắt Đầu Cướp Giáo Hoa Nữ Chính [Dịch]</t>
+          <t>Thần Tuyển Lạc Viên [Dịch]</t>
         </is>
       </c>
       <c r="F827" t="inlineStr">
         <is>
-          <t>Đô Thị, Hệ Thống, Phản Phái, Mạt Thế</t>
+          <t>Đô Thị, Võng Du, Hệ Thống, Dị Năng</t>
         </is>
       </c>
       <c r="G827" t="inlineStr">
@@ -38451,7 +38451,7 @@
         </is>
       </c>
       <c r="H827" t="n">
-        <v>10.5833</v>
+        <v>12.8846</v>
       </c>
       <c r="I827" t="inlineStr">
         <is>
@@ -38460,7 +38460,7 @@
       </c>
       <c r="J827" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/19676-tan-the-phan-phai-bat-dau-cuop-giao-hoa-nu-chinh-dich</t>
+          <t>https://sitruyencv.com/story/19019-than-tuyen-lac-vien-dich</t>
         </is>
       </c>
     </row>
@@ -38472,23 +38472,23 @@
       </c>
       <c r="B828" t="inlineStr">
         <is>
-          <t>Tìm truyện mà vừa có hệ thống vừa phát triển thế lực và main cơ trí.</t>
+          <t>Tìm truyện mà vừa có hệ thống vừa phát triển thế lực, main cơ trí và có trạng thái đang ra</t>
         </is>
       </c>
       <c r="C828" t="n">
         <v>7</v>
       </c>
       <c r="D828" t="n">
-        <v>13681</v>
+        <v>19931</v>
       </c>
       <c r="E828" t="inlineStr">
         <is>
-          <t>Conan: Suy Luận? Không, Ta Trực Tiếp Tốc Thông [Convert]</t>
+          <t>Hồng Lâu: Từ Đứa Chăn Trâu Bắt Đầu! [Convert]</t>
         </is>
       </c>
       <c r="F828" t="inlineStr">
         <is>
-          <t>Đồng Nhân</t>
+          <t>Dã Sử</t>
         </is>
       </c>
       <c r="G828" t="inlineStr">
@@ -38497,7 +38497,7 @@
         </is>
       </c>
       <c r="H828" t="n">
-        <v>10.4027</v>
+        <v>12.8102</v>
       </c>
       <c r="I828" t="inlineStr">
         <is>
@@ -38506,7 +38506,7 @@
       </c>
       <c r="J828" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/13681-conan-suy-luan-khong-ta-truc-tiep-toc-thong-convert</t>
+          <t>https://sitruyencv.com/story/19931-hong-lau-tu-dua-chan-trau-bat-dau-convert</t>
         </is>
       </c>
     </row>
@@ -38518,23 +38518,23 @@
       </c>
       <c r="B829" t="inlineStr">
         <is>
-          <t>Tìm truyện mà vừa có hệ thống vừa phát triển thế lực và main cơ trí.</t>
+          <t>Tìm truyện mà vừa có hệ thống vừa phát triển thế lực, main cơ trí và có trạng thái đang ra</t>
         </is>
       </c>
       <c r="C829" t="n">
         <v>8</v>
       </c>
       <c r="D829" t="n">
-        <v>19019</v>
+        <v>20392</v>
       </c>
       <c r="E829" t="inlineStr">
         <is>
-          <t>Thần Tuyển Lạc Viên [Dịch]</t>
+          <t>Nhà Ta Thế Hệ Cường Đạo, Tiểu Tử Ngươi Thi Đậu Trạng Nguyên [Dịch]</t>
         </is>
       </c>
       <c r="F829" t="inlineStr">
         <is>
-          <t>Đô Thị, Võng Du, Hệ Thống, Dị Năng</t>
+          <t>Huyền Huyễn, Cổ Đại</t>
         </is>
       </c>
       <c r="G829" t="inlineStr">
@@ -38543,7 +38543,7 @@
         </is>
       </c>
       <c r="H829" t="n">
-        <v>10.3084</v>
+        <v>12.5841</v>
       </c>
       <c r="I829" t="inlineStr">
         <is>
@@ -38552,7 +38552,7 @@
       </c>
       <c r="J829" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/19019-than-tuyen-lac-vien-dich</t>
+          <t>https://sitruyencv.com/story/20392-nha-ta-the-he-cuong-dao-tieu-tu-nguoi-thi-dau-trang-nguyen-dich</t>
         </is>
       </c>
     </row>
@@ -38564,18 +38564,18 @@
       </c>
       <c r="B830" t="inlineStr">
         <is>
-          <t>Tìm truyện mà vừa có hệ thống vừa phát triển thế lực và main cơ trí.</t>
+          <t>Tìm truyện mà vừa có hệ thống vừa phát triển thế lực, main cơ trí và có trạng thái đang ra</t>
         </is>
       </c>
       <c r="C830" t="n">
         <v>9</v>
       </c>
       <c r="D830" t="n">
-        <v>17058</v>
+        <v>13514</v>
       </c>
       <c r="E830" t="inlineStr">
         <is>
-          <t>Bắt Đầu Vừa Vặn Cẩu Hết Mười Năm, Ta Vô Địch [Convert]</t>
+          <t>Mạnh Nhất Gia Tộc, Từ Khai Chi Tán Diệp Bắt Đầu [Convert]</t>
         </is>
       </c>
       <c r="F830" t="inlineStr">
@@ -38589,7 +38589,7 @@
         </is>
       </c>
       <c r="H830" t="n">
-        <v>10.2309</v>
+        <v>12.443</v>
       </c>
       <c r="I830" t="inlineStr">
         <is>
@@ -38598,7 +38598,7 @@
       </c>
       <c r="J830" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/17058-bat-dau-vua-van-cau-het-muoi-nam-ta-vo-dich-convert</t>
+          <t>https://sitruyencv.com/story/13514-manh-nhat-gia-toc-tu-khai-chi-tan-diep-bat-dau-convert</t>
         </is>
       </c>
     </row>
@@ -38610,18 +38610,18 @@
       </c>
       <c r="B831" t="inlineStr">
         <is>
-          <t>Tìm truyện mà vừa có hệ thống vừa phát triển thế lực và main cơ trí.</t>
+          <t>Tìm truyện mà vừa có hệ thống vừa phát triển thế lực, main cơ trí và có trạng thái đang ra</t>
         </is>
       </c>
       <c r="C831" t="n">
         <v>10</v>
       </c>
       <c r="D831" t="n">
-        <v>13817</v>
+        <v>14011</v>
       </c>
       <c r="E831" t="inlineStr">
         <is>
-          <t>Phong Thần: Cự Tuyệt Liên Ngẫu Hóa Thân [Convert]</t>
+          <t>Phàm Nhân Tu Tiên, Bắt Đầu Nhặt Được Tụ Bảo Tiên Đỉnh [Convert]</t>
         </is>
       </c>
       <c r="F831" t="inlineStr">
@@ -38635,7 +38635,7 @@
         </is>
       </c>
       <c r="H831" t="n">
-        <v>9.561199999999999</v>
+        <v>11.3304</v>
       </c>
       <c r="I831" t="inlineStr">
         <is>
@@ -38644,7 +38644,7 @@
       </c>
       <c r="J831" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/13817-phong-than-cu-tuyet-lien-ngau-hoa-than-convert</t>
+          <t>https://sitruyencv.com/story/14011-pham-nhan-tu-tien-bat-dau-nhat-duoc-tu-bao-tien-dinh-convert</t>
         </is>
       </c>
     </row>
@@ -39116,7 +39116,7 @@
       </c>
       <c r="B842" t="inlineStr">
         <is>
-          <t>Hãy đề cử tôi truyện đồng nhân liên quan đến hải tặc hoặc là ninja, main có hệ thống phụ trợ càng tốt, đa tử đa phúc nữa</t>
+          <t>Hãy đề cử tôi truyện đồng nhân liên quan đến hải tặc hoặc là ninja, main có hệ thống phụ trợ càng tốt, đa tử đa phúc nữa có hơn 200 chương nha</t>
         </is>
       </c>
       <c r="C842" t="n">
@@ -39141,7 +39141,7 @@
         </is>
       </c>
       <c r="H842" t="n">
-        <v>24.2301</v>
+        <v>26.8792</v>
       </c>
       <c r="I842" t="inlineStr">
         <is>
@@ -39162,7 +39162,7 @@
       </c>
       <c r="B843" t="inlineStr">
         <is>
-          <t>Hãy đề cử tôi truyện đồng nhân liên quan đến hải tặc hoặc là ninja, main có hệ thống phụ trợ càng tốt, đa tử đa phúc nữa</t>
+          <t>Hãy đề cử tôi truyện đồng nhân liên quan đến hải tặc hoặc là ninja, main có hệ thống phụ trợ càng tốt, đa tử đa phúc nữa có hơn 200 chương nha</t>
         </is>
       </c>
       <c r="C843" t="n">
@@ -39208,18 +39208,18 @@
       </c>
       <c r="B844" t="inlineStr">
         <is>
-          <t>Hãy đề cử tôi truyện đồng nhân liên quan đến hải tặc hoặc là ninja, main có hệ thống phụ trợ càng tốt, đa tử đa phúc nữa</t>
+          <t>Hãy đề cử tôi truyện đồng nhân liên quan đến hải tặc hoặc là ninja, main có hệ thống phụ trợ càng tốt, đa tử đa phúc nữa có hơn 200 chương nha</t>
         </is>
       </c>
       <c r="C844" t="n">
         <v>3</v>
       </c>
       <c r="D844" t="n">
-        <v>7166</v>
+        <v>11918</v>
       </c>
       <c r="E844" t="inlineStr">
         <is>
-          <t>Muốn Chơi Thật Giả Thiếu Gia, Hỏi Qua Đao Của Ta Sao [Convert]</t>
+          <t>Ngự Thú Tiến Hóa Thương [Convert]</t>
         </is>
       </c>
       <c r="F844" t="inlineStr">
@@ -39233,7 +39233,7 @@
         </is>
       </c>
       <c r="H844" t="n">
-        <v>21.3689</v>
+        <v>21.4513</v>
       </c>
       <c r="I844" t="inlineStr">
         <is>
@@ -39242,7 +39242,7 @@
       </c>
       <c r="J844" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/7166-muon-choi-that-gia-thieu-gia-hoi-qua-dao-cua-ta-sao-convert</t>
+          <t>https://sitruyencv.com/story/11918-ngu-thu-tien-hoa-thuong-convert</t>
         </is>
       </c>
     </row>
@@ -39254,18 +39254,18 @@
       </c>
       <c r="B845" t="inlineStr">
         <is>
-          <t>Hãy đề cử tôi truyện đồng nhân liên quan đến hải tặc hoặc là ninja, main có hệ thống phụ trợ càng tốt, đa tử đa phúc nữa</t>
+          <t>Hãy đề cử tôi truyện đồng nhân liên quan đến hải tặc hoặc là ninja, main có hệ thống phụ trợ càng tốt, đa tử đa phúc nữa có hơn 200 chương nha</t>
         </is>
       </c>
       <c r="C845" t="n">
         <v>4</v>
       </c>
       <c r="D845" t="n">
-        <v>13514</v>
+        <v>7166</v>
       </c>
       <c r="E845" t="inlineStr">
         <is>
-          <t>Mạnh Nhất Gia Tộc, Từ Khai Chi Tán Diệp Bắt Đầu [Convert]</t>
+          <t>Muốn Chơi Thật Giả Thiếu Gia, Hỏi Qua Đao Của Ta Sao [Convert]</t>
         </is>
       </c>
       <c r="F845" t="inlineStr">
@@ -39275,11 +39275,11 @@
       </c>
       <c r="G845" t="inlineStr">
         <is>
-          <t>Đang ra</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="H845" t="n">
-        <v>18.8579</v>
+        <v>21.3689</v>
       </c>
       <c r="I845" t="inlineStr">
         <is>
@@ -39288,7 +39288,7 @@
       </c>
       <c r="J845" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/13514-manh-nhat-gia-toc-tu-khai-chi-tan-diep-bat-dau-convert</t>
+          <t>https://sitruyencv.com/story/7166-muon-choi-that-gia-thieu-gia-hoi-qua-dao-cua-ta-sao-convert</t>
         </is>
       </c>
     </row>
@@ -39300,32 +39300,32 @@
       </c>
       <c r="B846" t="inlineStr">
         <is>
-          <t>Hãy đề cử tôi truyện đồng nhân liên quan đến hải tặc hoặc là ninja, main có hệ thống phụ trợ càng tốt, đa tử đa phúc nữa</t>
+          <t>Hãy đề cử tôi truyện đồng nhân liên quan đến hải tặc hoặc là ninja, main có hệ thống phụ trợ càng tốt, đa tử đa phúc nữa có hơn 200 chương nha</t>
         </is>
       </c>
       <c r="C846" t="n">
         <v>5</v>
       </c>
       <c r="D846" t="n">
-        <v>13739</v>
+        <v>19019</v>
       </c>
       <c r="E846" t="inlineStr">
         <is>
-          <t>Đa Tử Đa Phúc, Bắt Đầu Liền Đưa Tuyệt Mỹ Lão Bà [Convert]</t>
+          <t>Thần Tuyển Lạc Viên [Dịch]</t>
         </is>
       </c>
       <c r="F846" t="inlineStr">
         <is>
-          <t>Dã Sử</t>
+          <t>Đô Thị, Võng Du, Hệ Thống, Dị Năng</t>
         </is>
       </c>
       <c r="G846" t="inlineStr">
         <is>
-          <t>Đang ra</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="H846" t="n">
-        <v>18.784</v>
+        <v>20.9051</v>
       </c>
       <c r="I846" t="inlineStr">
         <is>
@@ -39334,7 +39334,7 @@
       </c>
       <c r="J846" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/13739-da-tu-da-phuc-bat-dau-lien-dua-tuyet-my-lao-ba-convert</t>
+          <t>https://sitruyencv.com/story/19019-than-tuyen-lac-vien-dich</t>
         </is>
       </c>
     </row>
@@ -39346,18 +39346,18 @@
       </c>
       <c r="B847" t="inlineStr">
         <is>
-          <t>Hãy đề cử tôi truyện đồng nhân liên quan đến hải tặc hoặc là ninja, main có hệ thống phụ trợ càng tốt, đa tử đa phúc nữa</t>
+          <t>Hãy đề cử tôi truyện đồng nhân liên quan đến hải tặc hoặc là ninja, main có hệ thống phụ trợ càng tốt, đa tử đa phúc nữa có hơn 200 chương nha</t>
         </is>
       </c>
       <c r="C847" t="n">
         <v>6</v>
       </c>
       <c r="D847" t="n">
-        <v>11918</v>
+        <v>13514</v>
       </c>
       <c r="E847" t="inlineStr">
         <is>
-          <t>Ngự Thú Tiến Hóa Thương [Convert]</t>
+          <t>Mạnh Nhất Gia Tộc, Từ Khai Chi Tán Diệp Bắt Đầu [Convert]</t>
         </is>
       </c>
       <c r="F847" t="inlineStr">
@@ -39367,11 +39367,11 @@
       </c>
       <c r="G847" t="inlineStr">
         <is>
-          <t>Hoàn thành</t>
+          <t>Đang ra</t>
         </is>
       </c>
       <c r="H847" t="n">
-        <v>18.4172</v>
+        <v>18.8579</v>
       </c>
       <c r="I847" t="inlineStr">
         <is>
@@ -39380,7 +39380,7 @@
       </c>
       <c r="J847" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/11918-ngu-thu-tien-hoa-thuong-convert</t>
+          <t>https://sitruyencv.com/story/13514-manh-nhat-gia-toc-tu-khai-chi-tan-diep-bat-dau-convert</t>
         </is>
       </c>
     </row>
@@ -39392,23 +39392,23 @@
       </c>
       <c r="B848" t="inlineStr">
         <is>
-          <t>Hãy đề cử tôi truyện đồng nhân liên quan đến hải tặc hoặc là ninja, main có hệ thống phụ trợ càng tốt, đa tử đa phúc nữa</t>
+          <t>Hãy đề cử tôi truyện đồng nhân liên quan đến hải tặc hoặc là ninja, main có hệ thống phụ trợ càng tốt, đa tử đa phúc nữa có hơn 200 chương nha</t>
         </is>
       </c>
       <c r="C848" t="n">
         <v>7</v>
       </c>
       <c r="D848" t="n">
-        <v>19397</v>
+        <v>13739</v>
       </c>
       <c r="E848" t="inlineStr">
         <is>
-          <t>Đa Tử Đa Phúc, Thập Nhị Tổ Vu Bức Hôn Toàn Hồng Hoang [Convert]</t>
+          <t>Đa Tử Đa Phúc, Bắt Đầu Liền Đưa Tuyệt Mỹ Lão Bà [Convert]</t>
         </is>
       </c>
       <c r="F848" t="inlineStr">
         <is>
-          <t>Huyền Huyễn</t>
+          <t>Dã Sử</t>
         </is>
       </c>
       <c r="G848" t="inlineStr">
@@ -39417,7 +39417,7 @@
         </is>
       </c>
       <c r="H848" t="n">
-        <v>17.8828</v>
+        <v>18.784</v>
       </c>
       <c r="I848" t="inlineStr">
         <is>
@@ -39426,7 +39426,7 @@
       </c>
       <c r="J848" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/19397-da-tu-da-phuc-thap-nhi-to-vu-buc-hon-toan-hong-hoang-convert</t>
+          <t>https://sitruyencv.com/story/13739-da-tu-da-phuc-bat-dau-lien-dua-tuyet-my-lao-ba-convert</t>
         </is>
       </c>
     </row>
@@ -39438,18 +39438,18 @@
       </c>
       <c r="B849" t="inlineStr">
         <is>
-          <t>Hãy đề cử tôi truyện đồng nhân liên quan đến hải tặc hoặc là ninja, main có hệ thống phụ trợ càng tốt, đa tử đa phúc nữa</t>
+          <t>Hãy đề cử tôi truyện đồng nhân liên quan đến hải tặc hoặc là ninja, main có hệ thống phụ trợ càng tốt, đa tử đa phúc nữa có hơn 200 chương nha</t>
         </is>
       </c>
       <c r="C849" t="n">
         <v>8</v>
       </c>
       <c r="D849" t="n">
-        <v>20764</v>
+        <v>19397</v>
       </c>
       <c r="E849" t="inlineStr">
         <is>
-          <t>Đa Tử Đa Phúc, Ta Hiến Dâng Chính Mình Cho Tông Môn [Dịch]</t>
+          <t>Đa Tử Đa Phúc, Thập Nhị Tổ Vu Bức Hôn Toàn Hồng Hoang [Convert]</t>
         </is>
       </c>
       <c r="F849" t="inlineStr">
@@ -39459,11 +39459,11 @@
       </c>
       <c r="G849" t="inlineStr">
         <is>
-          <t>Hoàn thành</t>
+          <t>Đang ra</t>
         </is>
       </c>
       <c r="H849" t="n">
-        <v>17.6467</v>
+        <v>17.8828</v>
       </c>
       <c r="I849" t="inlineStr">
         <is>
@@ -39472,7 +39472,7 @@
       </c>
       <c r="J849" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/20764-da-tu-da-phuc-ta-hien-dang-chinh-minh-cho-tong-mon-dich</t>
+          <t>https://sitruyencv.com/story/19397-da-tu-da-phuc-thap-nhi-to-vu-buc-hon-toan-hong-hoang-convert</t>
         </is>
       </c>
     </row>
@@ -39484,32 +39484,32 @@
       </c>
       <c r="B850" t="inlineStr">
         <is>
-          <t>Hãy đề cử tôi truyện đồng nhân liên quan đến hải tặc hoặc là ninja, main có hệ thống phụ trợ càng tốt, đa tử đa phúc nữa</t>
+          <t>Hãy đề cử tôi truyện đồng nhân liên quan đến hải tặc hoặc là ninja, main có hệ thống phụ trợ càng tốt, đa tử đa phúc nữa có hơn 200 chương nha</t>
         </is>
       </c>
       <c r="C850" t="n">
         <v>9</v>
       </c>
       <c r="D850" t="n">
-        <v>15086</v>
+        <v>20764</v>
       </c>
       <c r="E850" t="inlineStr">
         <is>
-          <t>Hải Tặc: Ta, Rocks Trên Thuyền Chiến Lực Mạnh Nhất [Convert]</t>
+          <t>Đa Tử Đa Phúc, Ta Hiến Dâng Chính Mình Cho Tông Môn [Dịch]</t>
         </is>
       </c>
       <c r="F850" t="inlineStr">
         <is>
-          <t>Đồng Nhân</t>
+          <t>Huyền Huyễn</t>
         </is>
       </c>
       <c r="G850" t="inlineStr">
         <is>
-          <t>Đang ra</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="H850" t="n">
-        <v>17.031</v>
+        <v>17.6467</v>
       </c>
       <c r="I850" t="inlineStr">
         <is>
@@ -39518,7 +39518,7 @@
       </c>
       <c r="J850" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/15086-hai-tac-ta-rocks-tren-thuyen-chien-luc-manh-nhat-convert</t>
+          <t>https://sitruyencv.com/story/20764-da-tu-da-phuc-ta-hien-dang-chinh-minh-cho-tong-mon-dich</t>
         </is>
       </c>
     </row>
@@ -39530,23 +39530,23 @@
       </c>
       <c r="B851" t="inlineStr">
         <is>
-          <t>Hãy đề cử tôi truyện đồng nhân liên quan đến hải tặc hoặc là ninja, main có hệ thống phụ trợ càng tốt, đa tử đa phúc nữa</t>
+          <t>Hãy đề cử tôi truyện đồng nhân liên quan đến hải tặc hoặc là ninja, main có hệ thống phụ trợ càng tốt, đa tử đa phúc nữa có hơn 200 chương nha</t>
         </is>
       </c>
       <c r="C851" t="n">
         <v>10</v>
       </c>
       <c r="D851" t="n">
-        <v>14007</v>
+        <v>15086</v>
       </c>
       <c r="E851" t="inlineStr">
         <is>
-          <t>Cửu Giai phù Lục sư [Convert]</t>
+          <t>Hải Tặc: Ta, Rocks Trên Thuyền Chiến Lực Mạnh Nhất [Convert]</t>
         </is>
       </c>
       <c r="F851" t="inlineStr">
         <is>
-          <t>Tiên Hiệp</t>
+          <t>Đồng Nhân</t>
         </is>
       </c>
       <c r="G851" t="inlineStr">
@@ -39555,7 +39555,7 @@
         </is>
       </c>
       <c r="H851" t="n">
-        <v>16.8658</v>
+        <v>17.031</v>
       </c>
       <c r="I851" t="inlineStr">
         <is>
@@ -39564,7 +39564,7 @@
       </c>
       <c r="J851" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/14007-cuu-giai-phu-luc-su-convert</t>
+          <t>https://sitruyencv.com/story/15086-hai-tac-ta-rocks-tren-thuyen-chien-luc-manh-nhat-convert</t>
         </is>
       </c>
     </row>
@@ -44636,18 +44636,18 @@
       </c>
       <c r="B962" t="inlineStr">
         <is>
-          <t>Tìm truyện có nhân vật chính vô địch nhưng không có hệ thống</t>
+          <t>Tìm truyện có nhân vật chính vô địch nhưng không có hệ thống và có trạng thái đang ra</t>
         </is>
       </c>
       <c r="C962" t="n">
         <v>1</v>
       </c>
       <c r="D962" t="n">
-        <v>15905</v>
+        <v>11553</v>
       </c>
       <c r="E962" t="inlineStr">
         <is>
-          <t>Toàn Dân Đầu Tư Thời Đại: Chỉ Có Ta Biết Nhân Vật Chính [Convert]</t>
+          <t>Bắt Đầu Kém Chút Bị Ăn, May Mắn Ta Có Thể Dời Đi Mặt Trái Trạng Thái [Convert]</t>
         </is>
       </c>
       <c r="F962" t="inlineStr">
@@ -44661,7 +44661,7 @@
         </is>
       </c>
       <c r="H962" t="n">
-        <v>13.5501</v>
+        <v>16.7399</v>
       </c>
       <c r="I962" t="inlineStr">
         <is>
@@ -44670,7 +44670,7 @@
       </c>
       <c r="J962" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/15905-toan-dan-dau-tu-thoi-dai-chi-co-ta-biet-nhan-vat-chinh-convert</t>
+          <t>https://sitruyencv.com/story/11553-bat-dau-kem-chut-bi-an-may-man-ta-co-the-doi-di-mat-trai-trang-thai-convert</t>
         </is>
       </c>
     </row>
@@ -44682,32 +44682,32 @@
       </c>
       <c r="B963" t="inlineStr">
         <is>
-          <t>Tìm truyện có nhân vật chính vô địch nhưng không có hệ thống</t>
+          <t>Tìm truyện có nhân vật chính vô địch nhưng không có hệ thống và có trạng thái đang ra</t>
         </is>
       </c>
       <c r="C963" t="n">
         <v>2</v>
       </c>
       <c r="D963" t="n">
-        <v>13237</v>
+        <v>19019</v>
       </c>
       <c r="E963" t="inlineStr">
         <is>
-          <t>Kinh Tiêu [Convert]</t>
+          <t>Thần Tuyển Lạc Viên [Dịch]</t>
         </is>
       </c>
       <c r="F963" t="inlineStr">
         <is>
-          <t>Huyền Huyễn</t>
+          <t>Đô Thị, Võng Du, Hệ Thống, Dị Năng</t>
         </is>
       </c>
       <c r="G963" t="inlineStr">
         <is>
-          <t>Đang ra</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="H963" t="n">
-        <v>12.2572</v>
+        <v>15.7984</v>
       </c>
       <c r="I963" t="inlineStr">
         <is>
@@ -44716,7 +44716,7 @@
       </c>
       <c r="J963" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/13237-kinh-tieu-convert</t>
+          <t>https://sitruyencv.com/story/19019-than-tuyen-lac-vien-dich</t>
         </is>
       </c>
     </row>
@@ -44728,32 +44728,32 @@
       </c>
       <c r="B964" t="inlineStr">
         <is>
-          <t>Tìm truyện có nhân vật chính vô địch nhưng không có hệ thống</t>
+          <t>Tìm truyện có nhân vật chính vô địch nhưng không có hệ thống và có trạng thái đang ra</t>
         </is>
       </c>
       <c r="C964" t="n">
         <v>3</v>
       </c>
       <c r="D964" t="n">
-        <v>19019</v>
+        <v>18457</v>
       </c>
       <c r="E964" t="inlineStr">
         <is>
-          <t>Thần Tuyển Lạc Viên [Dịch]</t>
+          <t>Thiên Băng Khai Cục, Từ Tử Tù Doanh Chém Tới Chiến Vương [Dịch]</t>
         </is>
       </c>
       <c r="F964" t="inlineStr">
         <is>
-          <t>Đô Thị, Võng Du, Hệ Thống, Dị Năng</t>
+          <t>Hệ Thống, Lịch Sử Quân Sự, Xuyên Sách</t>
         </is>
       </c>
       <c r="G964" t="inlineStr">
         <is>
-          <t>Hoàn thành</t>
+          <t>Đang ra</t>
         </is>
       </c>
       <c r="H964" t="n">
-        <v>12.2437</v>
+        <v>14.5461</v>
       </c>
       <c r="I964" t="inlineStr">
         <is>
@@ -44762,7 +44762,7 @@
       </c>
       <c r="J964" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/19019-than-tuyen-lac-vien-dich</t>
+          <t>https://sitruyencv.com/story/18457-thien-bang-khai-cuc-tu-tu-tu-doanh-chem-toi-chien-vuong-dich</t>
         </is>
       </c>
     </row>
@@ -44774,32 +44774,32 @@
       </c>
       <c r="B965" t="inlineStr">
         <is>
-          <t>Tìm truyện có nhân vật chính vô địch nhưng không có hệ thống</t>
+          <t>Tìm truyện có nhân vật chính vô địch nhưng không có hệ thống và có trạng thái đang ra</t>
         </is>
       </c>
       <c r="C965" t="n">
         <v>4</v>
       </c>
       <c r="D965" t="n">
-        <v>20772</v>
+        <v>15905</v>
       </c>
       <c r="E965" t="inlineStr">
         <is>
-          <t>Hệ Thống: Để Ngươi Giúp Đồ Đệ Mạnh Lên, Không Có Để Ngươi Vô Địch [Dịch]</t>
+          <t>Toàn Dân Đầu Tư Thời Đại: Chỉ Có Ta Biết Nhân Vật Chính [Convert]</t>
         </is>
       </c>
       <c r="F965" t="inlineStr">
         <is>
-          <t>Tiên Hiệp, Huyền Huyễn, Hệ Thống</t>
+          <t>Huyền Huyễn</t>
         </is>
       </c>
       <c r="G965" t="inlineStr">
         <is>
-          <t>Hoàn thành</t>
+          <t>Đang ra</t>
         </is>
       </c>
       <c r="H965" t="n">
-        <v>12.2296</v>
+        <v>14.1519</v>
       </c>
       <c r="I965" t="inlineStr">
         <is>
@@ -44808,7 +44808,7 @@
       </c>
       <c r="J965" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/20772-he-thong-de-nguoi-giup-do-de-manh-len-khong-co-de-nguoi-vo-dich-dich</t>
+          <t>https://sitruyencv.com/story/15905-toan-dan-dau-tu-thoi-dai-chi-co-ta-biet-nhan-vat-chinh-convert</t>
         </is>
       </c>
     </row>
@@ -44820,7 +44820,7 @@
       </c>
       <c r="B966" t="inlineStr">
         <is>
-          <t>Tìm truyện có nhân vật chính vô địch nhưng không có hệ thống</t>
+          <t>Tìm truyện có nhân vật chính vô địch nhưng không có hệ thống và có trạng thái đang ra</t>
         </is>
       </c>
       <c r="C966" t="n">
@@ -44845,7 +44845,7 @@
         </is>
       </c>
       <c r="H966" t="n">
-        <v>11.4049</v>
+        <v>13.7816</v>
       </c>
       <c r="I966" t="inlineStr">
         <is>
@@ -44866,23 +44866,23 @@
       </c>
       <c r="B967" t="inlineStr">
         <is>
-          <t>Tìm truyện có nhân vật chính vô địch nhưng không có hệ thống</t>
+          <t>Tìm truyện có nhân vật chính vô địch nhưng không có hệ thống và có trạng thái đang ra</t>
         </is>
       </c>
       <c r="C967" t="n">
         <v>6</v>
       </c>
       <c r="D967" t="n">
-        <v>12428</v>
+        <v>18864</v>
       </c>
       <c r="E967" t="inlineStr">
         <is>
-          <t>Đấu La: Thần Cấp Máy Gian Lận, Rời Núi Tức Vô Địch [Convert]</t>
+          <t>Thái Thượng Võ Thần Quyết [Convert]</t>
         </is>
       </c>
       <c r="F967" t="inlineStr">
         <is>
-          <t>Đồng Nhân</t>
+          <t>Huyền Huyễn</t>
         </is>
       </c>
       <c r="G967" t="inlineStr">
@@ -44891,7 +44891,7 @@
         </is>
       </c>
       <c r="H967" t="n">
-        <v>11.3367</v>
+        <v>13.3508</v>
       </c>
       <c r="I967" t="inlineStr">
         <is>
@@ -44900,7 +44900,7 @@
       </c>
       <c r="J967" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/12428-dau-la-than-cap-may-gian-lan-roi-nui-tuc-vo-dich-convert</t>
+          <t>https://sitruyencv.com/story/18864-thai-thuong-vo-than-quyet-convert</t>
         </is>
       </c>
     </row>
@@ -44912,23 +44912,23 @@
       </c>
       <c r="B968" t="inlineStr">
         <is>
-          <t>Tìm truyện có nhân vật chính vô địch nhưng không có hệ thống</t>
+          <t>Tìm truyện có nhân vật chính vô địch nhưng không có hệ thống và có trạng thái đang ra</t>
         </is>
       </c>
       <c r="C968" t="n">
         <v>7</v>
       </c>
       <c r="D968" t="n">
-        <v>19831</v>
+        <v>13623</v>
       </c>
       <c r="E968" t="inlineStr">
         <is>
-          <t>Đã Nói Từ Hôn, Sư Đồ Các Nàng Lại Hối Hận Muốn Gả Cho Ta [Convert]</t>
+          <t>Cái Gì Phản Phái Nam Phụ, Rõ Ràng Là Sư Huynh Ấm Áp! [Convert]</t>
         </is>
       </c>
       <c r="F968" t="inlineStr">
         <is>
-          <t>Tiên Hiệp</t>
+          <t>Huyền Huyễn</t>
         </is>
       </c>
       <c r="G968" t="inlineStr">
@@ -44937,7 +44937,7 @@
         </is>
       </c>
       <c r="H968" t="n">
-        <v>11.1562</v>
+        <v>12.5688</v>
       </c>
       <c r="I968" t="inlineStr">
         <is>
@@ -44946,7 +44946,7 @@
       </c>
       <c r="J968" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/19831-da-noi-tu-hon-su-do-cac-nang-lai-hoi-han-muon-ga-cho-ta-convert</t>
+          <t>https://sitruyencv.com/story/13623-cai-gi-phan-phai-nam-phu-ro-rang-la-su-huynh-am-ap-convert</t>
         </is>
       </c>
     </row>
@@ -44958,18 +44958,18 @@
       </c>
       <c r="B969" t="inlineStr">
         <is>
-          <t>Tìm truyện có nhân vật chính vô địch nhưng không có hệ thống</t>
+          <t>Tìm truyện có nhân vật chính vô địch nhưng không có hệ thống và có trạng thái đang ra</t>
         </is>
       </c>
       <c r="C969" t="n">
         <v>8</v>
       </c>
       <c r="D969" t="n">
-        <v>16145</v>
+        <v>12674</v>
       </c>
       <c r="E969" t="inlineStr">
         <is>
-          <t>Liếm Cẩu Phản Diện Chỉ Nghĩ Cẩu , Nữ Chính Không Theo Sáo Lộ Đi [Convert]</t>
+          <t>Quá Tốt Rồi, Là Biến Thái Hàng Xóm, Chúng Ta Không Cứu Nổi [Convert]</t>
         </is>
       </c>
       <c r="F969" t="inlineStr">
@@ -44983,7 +44983,7 @@
         </is>
       </c>
       <c r="H969" t="n">
-        <v>10.5642</v>
+        <v>12.3846</v>
       </c>
       <c r="I969" t="inlineStr">
         <is>
@@ -44992,7 +44992,7 @@
       </c>
       <c r="J969" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/16145-liem-cau-phan-dien-chi-nghi-cau-nu-chinh-khong-theo-sao-lo-di-convert</t>
+          <t>https://sitruyencv.com/story/12674-qua-tot-roi-la-bien-thai-hang-xom-chung-ta-khong-cuu-noi-convert</t>
         </is>
       </c>
     </row>
@@ -45004,32 +45004,32 @@
       </c>
       <c r="B970" t="inlineStr">
         <is>
-          <t>Tìm truyện có nhân vật chính vô địch nhưng không có hệ thống</t>
+          <t>Tìm truyện có nhân vật chính vô địch nhưng không có hệ thống và có trạng thái đang ra</t>
         </is>
       </c>
       <c r="C970" t="n">
         <v>9</v>
       </c>
       <c r="D970" t="n">
-        <v>16144</v>
+        <v>13237</v>
       </c>
       <c r="E970" t="inlineStr">
         <is>
-          <t>Hệ Thống Sợ Ta Tận Thế Chết, Bắt Đầu Đánh Dấu Allspark [Convert]</t>
+          <t>Kinh Tiêu [Convert]</t>
         </is>
       </c>
       <c r="F970" t="inlineStr">
         <is>
-          <t>Đô Thị</t>
+          <t>Huyền Huyễn</t>
         </is>
       </c>
       <c r="G970" t="inlineStr">
         <is>
-          <t>Hoàn thành</t>
+          <t>Đang ra</t>
         </is>
       </c>
       <c r="H970" t="n">
-        <v>10.3348</v>
+        <v>12.2572</v>
       </c>
       <c r="I970" t="inlineStr">
         <is>
@@ -45038,7 +45038,7 @@
       </c>
       <c r="J970" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/16144-he-thong-so-ta-tan-the-chet-bat-dau-danh-dau-allspark-convert</t>
+          <t>https://sitruyencv.com/story/13237-kinh-tieu-convert</t>
         </is>
       </c>
     </row>
@@ -45050,23 +45050,23 @@
       </c>
       <c r="B971" t="inlineStr">
         <is>
-          <t>Tìm truyện có nhân vật chính vô địch nhưng không có hệ thống</t>
+          <t>Tìm truyện có nhân vật chính vô địch nhưng không có hệ thống và có trạng thái đang ra</t>
         </is>
       </c>
       <c r="C971" t="n">
         <v>10</v>
       </c>
       <c r="D971" t="n">
-        <v>6628</v>
+        <v>20772</v>
       </c>
       <c r="E971" t="inlineStr">
         <is>
-          <t>Đi Biển Bắt Hải Sản: Ta Dựa Vào Vô Địch Vận Khí, Nhận Thầu Toàn Bộ Biển Cả [Convert]</t>
+          <t>Hệ Thống: Để Ngươi Giúp Đồ Đệ Mạnh Lên, Không Có Để Ngươi Vô Địch [Dịch]</t>
         </is>
       </c>
       <c r="F971" t="inlineStr">
         <is>
-          <t>Đô Thị</t>
+          <t>Tiên Hiệp, Huyền Huyễn, Hệ Thống</t>
         </is>
       </c>
       <c r="G971" t="inlineStr">
@@ -45075,7 +45075,7 @@
         </is>
       </c>
       <c r="H971" t="n">
-        <v>10.1209</v>
+        <v>12.2296</v>
       </c>
       <c r="I971" t="inlineStr">
         <is>
@@ -45084,7 +45084,7 @@
       </c>
       <c r="J971" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/6628-di-bien-bat-hai-san-ta-dua-vao-vo-dich-van-khi-nhan-thau-toan-bo-bien-ca-convert</t>
+          <t>https://sitruyencv.com/story/20772-he-thong-de-nguoi-giup-do-de-manh-len-khong-co-de-nguoi-vo-dich-dich</t>
         </is>
       </c>
     </row>
@@ -45096,7 +45096,7 @@
       </c>
       <c r="B972" t="inlineStr">
         <is>
-          <t>Tìm truyện xây dựng thế lực nhưng không có yếu tố đô thị</t>
+          <t>Tìm truyện xây dựng thế lực nhưng không có yếu tố đô thị và có nhiều hơn 300 chương</t>
         </is>
       </c>
       <c r="C972" t="n">
@@ -45142,18 +45142,18 @@
       </c>
       <c r="B973" t="inlineStr">
         <is>
-          <t>Tìm truyện xây dựng thế lực nhưng không có yếu tố đô thị</t>
+          <t>Tìm truyện xây dựng thế lực nhưng không có yếu tố đô thị và có nhiều hơn 300 chương</t>
         </is>
       </c>
       <c r="C973" t="n">
         <v>2</v>
       </c>
       <c r="D973" t="n">
-        <v>447</v>
+        <v>13674</v>
       </c>
       <c r="E973" t="inlineStr">
         <is>
-          <t>Chưởng Môn Chinh Đồ [Convert]</t>
+          <t>Vạn Thú Thế Gia Quật Khởi [Convert]</t>
         </is>
       </c>
       <c r="F973" t="inlineStr">
@@ -45163,11 +45163,11 @@
       </c>
       <c r="G973" t="inlineStr">
         <is>
-          <t>Hoàn thành</t>
+          <t>Đang ra</t>
         </is>
       </c>
       <c r="H973" t="n">
-        <v>13.61</v>
+        <v>16.7807</v>
       </c>
       <c r="I973" t="inlineStr">
         <is>
@@ -45176,7 +45176,7 @@
       </c>
       <c r="J973" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/447-chuong-mon-chinh-do-convert</t>
+          <t>https://sitruyencv.com/story/13674-van-thu-the-gia-quat-khoi-convert</t>
         </is>
       </c>
     </row>
@@ -45188,32 +45188,32 @@
       </c>
       <c r="B974" t="inlineStr">
         <is>
-          <t>Tìm truyện xây dựng thế lực nhưng không có yếu tố đô thị</t>
+          <t>Tìm truyện xây dựng thế lực nhưng không có yếu tố đô thị và có nhiều hơn 300 chương</t>
         </is>
       </c>
       <c r="C974" t="n">
         <v>3</v>
       </c>
       <c r="D974" t="n">
-        <v>19376</v>
+        <v>19395</v>
       </c>
       <c r="E974" t="inlineStr">
         <is>
-          <t>Toàn Dân Cầu Sinh: Khởi Đầu Trăm Lần Tốc Độ Tu Luyện [Dịch]</t>
+          <t>Trong Thôn Có Một Tu Tiên Tông Môn [Convert]</t>
         </is>
       </c>
       <c r="F974" t="inlineStr">
         <is>
-          <t>Đô Thị, Khoa Huyễn, Hệ Thống, Mạt Thế</t>
+          <t>Tiên Hiệp</t>
         </is>
       </c>
       <c r="G974" t="inlineStr">
         <is>
-          <t>Hoàn thành</t>
+          <t>Đang ra</t>
         </is>
       </c>
       <c r="H974" t="n">
-        <v>13.0535</v>
+        <v>16.2952</v>
       </c>
       <c r="I974" t="inlineStr">
         <is>
@@ -45222,7 +45222,7 @@
       </c>
       <c r="J974" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/19376-toan-dan-cau-sinh-khoi-dau-tram-lan-toc-do-tu-luyen-dich</t>
+          <t>https://sitruyencv.com/story/19395-trong-thon-co-mot-tu-tien-tong-mon-convert</t>
         </is>
       </c>
     </row>
@@ -45234,23 +45234,23 @@
       </c>
       <c r="B975" t="inlineStr">
         <is>
-          <t>Tìm truyện xây dựng thế lực nhưng không có yếu tố đô thị</t>
+          <t>Tìm truyện xây dựng thế lực nhưng không có yếu tố đô thị và có nhiều hơn 300 chương</t>
         </is>
       </c>
       <c r="C975" t="n">
         <v>4</v>
       </c>
       <c r="D975" t="n">
-        <v>10433</v>
+        <v>9529</v>
       </c>
       <c r="E975" t="inlineStr">
         <is>
-          <t>Thần Minh Máy Mô Phỏng [Convert]</t>
+          <t>Trực Tiếp Thiết Kế Tử Vong [Convert]</t>
         </is>
       </c>
       <c r="F975" t="inlineStr">
         <is>
-          <t>Khoa Huyễn</t>
+          <t>Đô Thị</t>
         </is>
       </c>
       <c r="G975" t="inlineStr">
@@ -45259,7 +45259,7 @@
         </is>
       </c>
       <c r="H975" t="n">
-        <v>12.5368</v>
+        <v>15.6677</v>
       </c>
       <c r="I975" t="inlineStr">
         <is>
@@ -45268,7 +45268,7 @@
       </c>
       <c r="J975" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/10433-than-minh-may-mo-phong-convert</t>
+          <t>https://sitruyencv.com/story/9529-truc-tiep-thiet-ke-tu-vong-convert</t>
         </is>
       </c>
     </row>
@@ -45280,32 +45280,32 @@
       </c>
       <c r="B976" t="inlineStr">
         <is>
-          <t>Tìm truyện xây dựng thế lực nhưng không có yếu tố đô thị</t>
+          <t>Tìm truyện xây dựng thế lực nhưng không có yếu tố đô thị và có nhiều hơn 300 chương</t>
         </is>
       </c>
       <c r="C976" t="n">
         <v>5</v>
       </c>
       <c r="D976" t="n">
-        <v>15093</v>
+        <v>20043</v>
       </c>
       <c r="E976" t="inlineStr">
         <is>
-          <t>Ngộ Tính Nghịch Thiên, Ta Ở Hogwarts Xây Phù Không Thành [Convert]</t>
+          <t>Giải Trí: Cùng Các Minh Tinh Sin Tồn Trên Hoang Đảo [Dịch]</t>
         </is>
       </c>
       <c r="F976" t="inlineStr">
         <is>
-          <t>Huyền Huyễn</t>
+          <t>Đô Thị, Kỳ Ảo, Hệ Thống, Tây Phương Kỳ Huyễn, Biến Thân, Điền Văn, Ngôn Tình, Nữ Phụ, Hiện Đại Ngôn Tình, Lãng Mạn Thanh Xuân</t>
         </is>
       </c>
       <c r="G976" t="inlineStr">
         <is>
-          <t>Đang ra</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="H976" t="n">
-        <v>12.5045</v>
+        <v>14.1843</v>
       </c>
       <c r="I976" t="inlineStr">
         <is>
@@ -45314,7 +45314,7 @@
       </c>
       <c r="J976" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/15093-ngo-tinh-nghich-thien-ta-o-hogwarts-xay-phu-khong-thanh-convert</t>
+          <t>https://sitruyencv.com/story/20043-giai-tri-cung-cac-minh-tinh-sin-ton-tren-hoang-dao-dich</t>
         </is>
       </c>
     </row>
@@ -45326,18 +45326,18 @@
       </c>
       <c r="B977" t="inlineStr">
         <is>
-          <t>Tìm truyện xây dựng thế lực nhưng không có yếu tố đô thị</t>
+          <t>Tìm truyện xây dựng thế lực nhưng không có yếu tố đô thị và có nhiều hơn 300 chương</t>
         </is>
       </c>
       <c r="C977" t="n">
         <v>6</v>
       </c>
       <c r="D977" t="n">
-        <v>19395</v>
+        <v>447</v>
       </c>
       <c r="E977" t="inlineStr">
         <is>
-          <t>Trong Thôn Có Một Tu Tiên Tông Môn [Convert]</t>
+          <t>Chưởng Môn Chinh Đồ [Convert]</t>
         </is>
       </c>
       <c r="F977" t="inlineStr">
@@ -45347,11 +45347,11 @@
       </c>
       <c r="G977" t="inlineStr">
         <is>
-          <t>Đang ra</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="H977" t="n">
-        <v>12.4068</v>
+        <v>13.61</v>
       </c>
       <c r="I977" t="inlineStr">
         <is>
@@ -45360,7 +45360,7 @@
       </c>
       <c r="J977" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/19395-trong-thon-co-mot-tu-tien-tong-mon-convert</t>
+          <t>https://sitruyencv.com/story/447-chuong-mon-chinh-do-convert</t>
         </is>
       </c>
     </row>
@@ -45372,32 +45372,32 @@
       </c>
       <c r="B978" t="inlineStr">
         <is>
-          <t>Tìm truyện xây dựng thế lực nhưng không có yếu tố đô thị</t>
+          <t>Tìm truyện xây dựng thế lực nhưng không có yếu tố đô thị và có nhiều hơn 300 chương</t>
         </is>
       </c>
       <c r="C978" t="n">
         <v>7</v>
       </c>
       <c r="D978" t="n">
-        <v>13674</v>
+        <v>16201</v>
       </c>
       <c r="E978" t="inlineStr">
         <is>
-          <t>Vạn Thú Thế Gia Quật Khởi [Convert]</t>
+          <t>Nữ Hiệp Xin Dừng Tay [Convert]</t>
         </is>
       </c>
       <c r="F978" t="inlineStr">
         <is>
-          <t>Tiên Hiệp</t>
+          <t>Dã Sử</t>
         </is>
       </c>
       <c r="G978" t="inlineStr">
         <is>
-          <t>Đang ra</t>
+          <t>Tạm dừng</t>
         </is>
       </c>
       <c r="H978" t="n">
-        <v>12.2327</v>
+        <v>13.6046</v>
       </c>
       <c r="I978" t="inlineStr">
         <is>
@@ -45406,7 +45406,7 @@
       </c>
       <c r="J978" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/13674-van-thu-the-gia-quat-khoi-convert</t>
+          <t>https://sitruyencv.com/story/16201-nu-hiep-xin-dung-tay-convert</t>
         </is>
       </c>
     </row>
@@ -45418,23 +45418,23 @@
       </c>
       <c r="B979" t="inlineStr">
         <is>
-          <t>Tìm truyện xây dựng thế lực nhưng không có yếu tố đô thị</t>
+          <t>Tìm truyện xây dựng thế lực nhưng không có yếu tố đô thị và có nhiều hơn 300 chương</t>
         </is>
       </c>
       <c r="C979" t="n">
         <v>8</v>
       </c>
       <c r="D979" t="n">
-        <v>15839</v>
+        <v>20735</v>
       </c>
       <c r="E979" t="inlineStr">
         <is>
-          <t>Mệnh Còn Lại Hai Năm, Bảy Cái Tỷ Tỷ Quỳ Cầu Ta Tha Thứ [Convert]</t>
+          <t>Tận thế: Hệ thống của ta là Jarvis [Dịch]</t>
         </is>
       </c>
       <c r="F979" t="inlineStr">
         <is>
-          <t>Đô Thị</t>
+          <t>Đô Thị, Khoa Huyễn, Hệ Thống, Mạt Thế</t>
         </is>
       </c>
       <c r="G979" t="inlineStr">
@@ -45443,7 +45443,7 @@
         </is>
       </c>
       <c r="H979" t="n">
-        <v>12.1666</v>
+        <v>13.5356</v>
       </c>
       <c r="I979" t="inlineStr">
         <is>
@@ -45452,7 +45452,7 @@
       </c>
       <c r="J979" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/15839-menh-con-lai-hai-nam-bay-cai-ty-ty-quy-cau-ta-tha-thu-convert</t>
+          <t>https://sitruyencv.com/story/20735-tan-the-he-thong-cua-ta-la-jarvis-dich</t>
         </is>
       </c>
     </row>
@@ -45464,7 +45464,7 @@
       </c>
       <c r="B980" t="inlineStr">
         <is>
-          <t>Tìm truyện xây dựng thế lực nhưng không có yếu tố đô thị</t>
+          <t>Tìm truyện xây dựng thế lực nhưng không có yếu tố đô thị và có nhiều hơn 300 chương</t>
         </is>
       </c>
       <c r="C980" t="n">
@@ -45489,7 +45489,7 @@
         </is>
       </c>
       <c r="H980" t="n">
-        <v>12.0677</v>
+        <v>13.5343</v>
       </c>
       <c r="I980" t="inlineStr">
         <is>
@@ -45510,7 +45510,7 @@
       </c>
       <c r="B981" t="inlineStr">
         <is>
-          <t>Tìm truyện xây dựng thế lực nhưng không có yếu tố đô thị</t>
+          <t>Tìm truyện xây dựng thế lực nhưng không có yếu tố đô thị và có nhiều hơn 300 chương</t>
         </is>
       </c>
       <c r="C981" t="n">
@@ -45535,7 +45535,7 @@
         </is>
       </c>
       <c r="H981" t="n">
-        <v>11.9782</v>
+        <v>13.2906</v>
       </c>
       <c r="I981" t="inlineStr">
         <is>
